--- a/planilhas/relatorio_inadimplencia_modelo.xlsx
+++ b/planilhas/relatorio_inadimplencia_modelo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabm\OneDrive\Documentos\projeto_ativuz\docx_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karol/Documents/Dashboard-Ativuz/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F9C9A1-609A-4A28-8E78-7CF29066936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386AB150-C236-1D41-ADFE-B686F1E5828B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo Executivo" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
   <si>
     <t>RELATÓRIO DE INADIMPLÊNCIA</t>
   </si>
@@ -74,9 +74,6 @@
     <t>JUROS MORA</t>
   </si>
   <si>
-    <t>PRÓXIMA AÇÃO</t>
-  </si>
-  <si>
     <t>RICARDO ARAUJO DE MIRANDA</t>
   </si>
   <si>
@@ -86,9 +83,6 @@
     <t>08/10/2025</t>
   </si>
   <si>
-    <t>Recolhimento + protesto em cartório + execução contratual</t>
-  </si>
-  <si>
     <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
@@ -104,9 +98,6 @@
     <t>15/02/2026</t>
   </si>
   <si>
-    <t>Notificação extrajudicial</t>
-  </si>
-  <si>
     <t>NOME DO CLIENTE 4</t>
   </si>
   <si>
@@ -116,9 +107,6 @@
     <t>20/01/2026</t>
   </si>
   <si>
-    <t>Protesto em cartório</t>
-  </si>
-  <si>
     <t>NOME DO CLIENTE 5</t>
   </si>
   <si>
@@ -126,9 +114,6 @@
   </si>
   <si>
     <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>Contato telefônico</t>
   </si>
   <si>
     <t>TOTAIS</t>
@@ -180,7 +165,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,78 +178,85 @@
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFAAAAAA"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF2C3E50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF2E86C1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFC0392B"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1E8449"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF2C3E50"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF7F8C8D"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -390,7 +382,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -446,11 +438,397 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1A3A5C"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1A3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1A3A5C"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1A3A5C"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1A3A5C"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1A3A5C"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1A3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1A3A5C"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1A3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -461,9 +839,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -476,9 +851,6 @@
     <xf numFmtId="164" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -487,118 +859,264 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -902,8 +1420,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="40.6640625" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" customWidth="1"/>
@@ -915,74 +1433,83 @@
     <col min="9" max="9" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+    <row r="1" spans="1:9" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="98"/>
+    </row>
+    <row r="2" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="98"/>
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-    </row>
-    <row r="3" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+    </row>
+    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="98"/>
+      <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-    </row>
-    <row r="4" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="49" t="s">
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+    </row>
+    <row r="4" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="98"/>
+      <c r="B4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="31" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="37" t="s">
+      <c r="F4" s="43"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="45"/>
-    </row>
-    <row r="5" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="50">
+      <c r="I4" s="35"/>
+    </row>
+    <row r="5" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="98"/>
+      <c r="B5" s="28">
         <f>COUNTA(C9:C57)</f>
         <v>5</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="33">
         <f>SUM(E9:E57)</f>
         <v>498</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="34">
-        <f>SUM(G9:G57)</f>
+      <c r="D5" s="33"/>
+      <c r="E5" s="45">
+        <f>SUM(H9:H57)</f>
         <v>1031.3</v>
       </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="38">
-        <f>SUM(H9:H57)</f>
+      <c r="F5" s="46"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="36">
+        <f>SUM(I9:I57)</f>
         <v>3291.3</v>
       </c>
-      <c r="I5" s="46"/>
-    </row>
-    <row r="6" spans="2:9" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
+      <c r="I5" s="37"/>
+    </row>
+    <row r="6" spans="1:9" ht="10" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="98"/>
+    </row>
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="98"/>
+      <c r="B7" s="99" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -994,635 +1521,730 @@
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="53"/>
+      <c r="H7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="98"/>
+      <c r="B8" s="95"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+    </row>
+    <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="98"/>
+      <c r="B9" s="96" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="E9" s="1">
         <v>218</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="101">
         <v>30</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="102"/>
+      <c r="H9" s="6">
         <v>32.700000000000003</v>
       </c>
-      <c r="H9" s="8">
+      <c r="I9" s="87">
         <v>62.7</v>
       </c>
-      <c r="I9" s="48" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="98"/>
+      <c r="B10" s="97" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="9" t="s">
+      <c r="E10" s="89">
+        <v>45</v>
+      </c>
+      <c r="F10" s="93">
+        <v>180</v>
+      </c>
+      <c r="G10" s="94"/>
+      <c r="H10" s="90">
+        <v>40.5</v>
+      </c>
+      <c r="I10" s="87">
+        <v>220.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="98"/>
+      <c r="B11" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="11">
-        <v>45</v>
-      </c>
-      <c r="F10" s="6">
-        <v>180</v>
-      </c>
-      <c r="G10" s="7">
-        <v>40.5</v>
-      </c>
-      <c r="H10" s="8">
-        <v>220.5</v>
-      </c>
-      <c r="I10" s="48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="E11" s="88">
+        <v>88</v>
+      </c>
+      <c r="F11" s="91">
+        <v>500</v>
+      </c>
+      <c r="G11" s="92"/>
+      <c r="H11" s="90">
+        <v>220</v>
+      </c>
+      <c r="I11" s="87">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="98"/>
+      <c r="B12" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="2">
-        <v>88</v>
-      </c>
-      <c r="F11" s="6">
-        <v>500</v>
-      </c>
-      <c r="G11" s="7">
-        <v>220</v>
-      </c>
-      <c r="H11" s="8">
-        <v>720</v>
-      </c>
-      <c r="I11" s="48" t="s">
+      <c r="D12" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
+      <c r="E12" s="88">
+        <v>113</v>
+      </c>
+      <c r="F12" s="91">
+        <v>1200</v>
+      </c>
+      <c r="G12" s="92"/>
+      <c r="H12" s="90">
+        <v>678.6</v>
+      </c>
+      <c r="I12" s="87">
+        <v>1878.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="98"/>
+      <c r="B13" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="2">
-        <v>113</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1200</v>
-      </c>
-      <c r="G12" s="7">
-        <v>678.6</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1878.6</v>
-      </c>
-      <c r="I12" s="48" t="s">
+      <c r="E13" s="89">
+        <v>34</v>
+      </c>
+      <c r="F13" s="93">
+        <v>350</v>
+      </c>
+      <c r="G13" s="94"/>
+      <c r="H13" s="90">
+        <v>59.5</v>
+      </c>
+      <c r="I13" s="87">
+        <v>409.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="98"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="85"/>
+    </row>
+    <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="98"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="86"/>
+    </row>
+    <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="98"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="85"/>
+    </row>
+    <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="98"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="86"/>
+    </row>
+    <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="98"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="85"/>
+    </row>
+    <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="98"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="86"/>
+    </row>
+    <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="98"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="85"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="98"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="86"/>
+    </row>
+    <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="98"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="85"/>
+    </row>
+    <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="98"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="86"/>
+    </row>
+    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="98"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="85"/>
+    </row>
+    <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="98"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="86"/>
+    </row>
+    <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="98"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="85"/>
+    </row>
+    <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="98"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="86"/>
+    </row>
+    <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="98"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="85"/>
+    </row>
+    <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="98"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="86"/>
+    </row>
+    <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="98"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="85"/>
+    </row>
+    <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="98"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="86"/>
+    </row>
+    <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="98"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="85"/>
+    </row>
+    <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="98"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="86"/>
+    </row>
+    <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="98"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="85"/>
+    </row>
+    <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="98"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="86"/>
+    </row>
+    <row r="36" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="98"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="85"/>
+    </row>
+    <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="98"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="86"/>
+    </row>
+    <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="98"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="85"/>
+    </row>
+    <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="98"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="86"/>
+    </row>
+    <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="98"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="85"/>
+    </row>
+    <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="98"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="86"/>
+    </row>
+    <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="98"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="85"/>
+    </row>
+    <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="98"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="86"/>
+    </row>
+    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="98"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="72"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="85"/>
+    </row>
+    <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="98"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="86"/>
+    </row>
+    <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="98"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="85"/>
+    </row>
+    <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="98"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="86"/>
+    </row>
+    <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="98"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="85"/>
+    </row>
+    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="98"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="86"/>
+    </row>
+    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="98"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="85"/>
+    </row>
+    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="98"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="86"/>
+    </row>
+    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="98"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="85"/>
+    </row>
+    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="98"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="86"/>
+    </row>
+    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="98"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="85"/>
+    </row>
+    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="98"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="51"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="86"/>
+    </row>
+    <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="98"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="50"/>
+      <c r="F56" s="72"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="85"/>
+    </row>
+    <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="98"/>
+      <c r="B57" s="103"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="68"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="103"/>
+      <c r="I57" s="111"/>
+    </row>
+    <row r="58" spans="1:10" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="98"/>
+      <c r="B58" s="105" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="11">
-        <v>34</v>
-      </c>
-      <c r="F13" s="6">
-        <v>350</v>
-      </c>
-      <c r="G13" s="7">
-        <v>59.5</v>
-      </c>
-      <c r="H13" s="8">
-        <v>409.5</v>
-      </c>
-      <c r="I13" s="48" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="48"/>
-    </row>
-    <row r="15" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="48"/>
-    </row>
-    <row r="16" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="48"/>
-    </row>
-    <row r="17" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="48"/>
-    </row>
-    <row r="18" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="48"/>
-    </row>
-    <row r="19" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="48"/>
-    </row>
-    <row r="20" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="48"/>
-    </row>
-    <row r="21" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="48"/>
-    </row>
-    <row r="22" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="48"/>
-    </row>
-    <row r="23" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="48"/>
-    </row>
-    <row r="24" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="48"/>
-    </row>
-    <row r="25" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="48"/>
-    </row>
-    <row r="26" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="48"/>
-    </row>
-    <row r="27" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="48"/>
-    </row>
-    <row r="28" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="48"/>
-    </row>
-    <row r="29" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="48"/>
-    </row>
-    <row r="30" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="48"/>
-    </row>
-    <row r="31" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="48"/>
-    </row>
-    <row r="32" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="48"/>
-    </row>
-    <row r="33" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="48"/>
-    </row>
-    <row r="34" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="48"/>
-    </row>
-    <row r="35" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="48"/>
-    </row>
-    <row r="36" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="48"/>
-    </row>
-    <row r="37" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="48"/>
-    </row>
-    <row r="38" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="48"/>
-    </row>
-    <row r="39" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="48"/>
-    </row>
-    <row r="40" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="48"/>
-    </row>
-    <row r="41" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="48"/>
-    </row>
-    <row r="42" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="48"/>
-    </row>
-    <row r="43" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="48"/>
-    </row>
-    <row r="44" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="48"/>
-    </row>
-    <row r="45" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="48"/>
-    </row>
-    <row r="46" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="48"/>
-    </row>
-    <row r="47" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="48"/>
-    </row>
-    <row r="48" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="48"/>
-    </row>
-    <row r="49" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="48"/>
-    </row>
-    <row r="50" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="48"/>
-    </row>
-    <row r="51" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="48"/>
-    </row>
-    <row r="52" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="48"/>
-    </row>
-    <row r="53" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="48"/>
-    </row>
-    <row r="54" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="48"/>
-    </row>
-    <row r="55" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="48"/>
-    </row>
-    <row r="56" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="48"/>
-    </row>
-    <row r="57" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="48"/>
-    </row>
-    <row r="58" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="14">
+      <c r="C58" s="106"/>
+      <c r="D58" s="106"/>
+      <c r="E58" s="107"/>
+      <c r="F58" s="108">
         <f>SUM(F9:F57)</f>
         <v>2260</v>
       </c>
-      <c r="G58" s="14">
-        <f>SUM(G9:G57)</f>
+      <c r="G58" s="109"/>
+      <c r="H58" s="110">
+        <f>SUM(H9:H57)</f>
         <v>1031.3</v>
       </c>
-      <c r="H58" s="14">
-        <f>SUM(H9:H57)</f>
+      <c r="I58" s="112">
+        <f>SUM(I9:I57)</f>
         <v>3291.3</v>
       </c>
-      <c r="I58" s="15"/>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B60" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
+      <c r="J58" s="100"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B60" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="61">
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="F7:G7"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1632,7 +2254,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:I12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1644,178 +2266,178 @@
     <col min="9" max="9" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-    </row>
-    <row r="4" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="2" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+    </row>
+    <row r="4" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="16"/>
-    </row>
-    <row r="6" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
+      <c r="I4" s="13"/>
+    </row>
+    <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D6" s="1">
         <v>218</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="5">
         <v>30</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>32.700000000000003</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>F6+G6</f>
         <v>62.7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="19" t="s">
-        <v>17</v>
+    <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="11">
+        <v>13</v>
+      </c>
+      <c r="D7" s="9">
         <v>45</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="5">
         <v>180</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>40.5</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <f>F7+G7</f>
         <v>220.5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="17" t="s">
-        <v>19</v>
+    <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2">
         <v>88</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5">
         <v>500</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>220</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <f>F8+G8</f>
         <v>720</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="19" t="s">
-        <v>23</v>
+    <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2">
         <v>113</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="E9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="5">
         <v>1200</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>678.6</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <f>F9+G9</f>
         <v>1878.6</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
-        <v>27</v>
+    <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="11">
+        <v>24</v>
+      </c>
+      <c r="D10" s="9">
         <v>34</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="5">
         <v>350</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>59.5</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <f>F10+G10</f>
         <v>409.5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="14">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="12">
         <f>SUM(F6:F11)</f>
         <v>2260</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="12">
         <f>SUM(G6:G11)</f>
         <v>1031.3</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="12">
         <f>SUM(H6:H11)</f>
         <v>3291.3</v>
       </c>
@@ -1832,7 +2454,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:G16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1841,210 +2463,210 @@
     <col min="7" max="7" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-    </row>
-    <row r="4" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16" t="s">
+    <row r="2" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="21">
+      <c r="G4" s="13"/>
+    </row>
+    <row r="6" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="18">
         <v>0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>0</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>0</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f t="shared" ref="F6:F14" si="0">D6+E6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="21">
+    <row r="7" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="18">
         <v>0</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>0</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>0</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="21">
+    <row r="8" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="18">
         <v>0</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>0</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>0</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="21">
+    <row r="9" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="18">
         <v>0</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>0</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>0</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="21">
+    <row r="10" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="18">
         <v>0</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>0</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>0</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="21">
+    <row r="11" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="18">
         <v>1</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>350</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>59.5</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <f t="shared" si="0"/>
         <v>409.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="21">
+    <row r="12" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="18">
         <v>1</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>1200</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>678.6</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <f t="shared" si="0"/>
         <v>1878.6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="21">
+    <row r="13" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="18">
         <v>1</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>500</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>220</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="21">
+    <row r="14" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="18">
         <v>3</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>210</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>73.2</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <f t="shared" si="0"/>
         <v>283.2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="14">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="12">
         <f>SUM(D6:D15)</f>
         <v>2260</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <f>SUM(E6:E15)</f>
         <v>1031.3</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="12">
         <f>SUM(F6:F15)</f>
         <v>3291.2999999999997</v>
       </c>

--- a/planilhas/relatorio_inadimplencia_modelo.xlsx
+++ b/planilhas/relatorio_inadimplencia_modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karol/Documents/Dashboard-Ativuz/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB5E428-DE95-B74F-A6AA-4FD74BCF2239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66176049-6713-8C4D-9DEF-F30CC05A77F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,7 +396,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -728,28 +728,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBDBDBD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBDBDBD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBDBDBD"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBDBDBD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </left>
@@ -825,25 +803,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBDBDBD"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBDBDBD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,14 +923,92 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="11" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -973,10 +1016,82 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -985,176 +1100,23 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="11" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1459,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="40.6640625" customWidth="1"/>
@@ -1477,71 +1439,71 @@
     </row>
     <row r="2" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="47"/>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="47"/>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
     </row>
     <row r="4" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="47"/>
       <c r="B4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="96" t="s">
+      <c r="C4" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="83" t="s">
+      <c r="D4" s="65"/>
+      <c r="E4" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="98" t="s">
+      <c r="F4" s="88"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="99"/>
+      <c r="I4" s="68"/>
     </row>
     <row r="5" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="47"/>
       <c r="B5" s="28">
-        <f>COUNTA(C9:C63)</f>
+        <f>COUNTA(C9:C70)</f>
         <v>5</v>
       </c>
-      <c r="C5" s="97">
-        <f>SUM(E9:E63)</f>
+      <c r="C5" s="66">
+        <f>SUM(E9:E70)</f>
         <v>498</v>
       </c>
-      <c r="D5" s="97"/>
-      <c r="E5" s="86">
-        <f>SUM(H9:H63)</f>
+      <c r="D5" s="66"/>
+      <c r="E5" s="90">
+        <f>SUM(H9:H70)</f>
         <v>1031.3</v>
       </c>
-      <c r="F5" s="87"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="100">
-        <f>SUM(I9:I63)</f>
+      <c r="F5" s="91"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="69">
+        <f>SUM(I9:I70)</f>
         <v>3291.3</v>
       </c>
-      <c r="I5" s="101"/>
+      <c r="I5" s="70"/>
     </row>
     <row r="6" spans="1:9" ht="10" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="47"/>
@@ -1560,10 +1522,10 @@
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="89" t="s">
+      <c r="F7" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="90"/>
+      <c r="G7" s="94"/>
       <c r="H7" s="3" t="s">
         <v>11</v>
       </c>
@@ -1590,14 +1552,14 @@
       <c r="E9" s="1">
         <v>218</v>
       </c>
-      <c r="F9" s="107">
+      <c r="F9" s="71">
         <v>30</v>
       </c>
-      <c r="G9" s="108"/>
-      <c r="H9" s="109">
+      <c r="G9" s="72"/>
+      <c r="H9" s="55">
         <v>32.700000000000003</v>
       </c>
-      <c r="I9" s="110">
+      <c r="I9" s="56">
         <v>62.7</v>
       </c>
     </row>
@@ -1615,14 +1577,14 @@
       <c r="E10" s="44">
         <v>45</v>
       </c>
-      <c r="F10" s="111">
+      <c r="F10" s="73">
         <v>180</v>
       </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="113">
+      <c r="G10" s="74"/>
+      <c r="H10" s="57">
         <v>40.5</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="56">
         <v>220.5</v>
       </c>
     </row>
@@ -1640,14 +1602,14 @@
       <c r="E11" s="43">
         <v>88</v>
       </c>
-      <c r="F11" s="114">
+      <c r="F11" s="75">
         <v>500</v>
       </c>
-      <c r="G11" s="115"/>
-      <c r="H11" s="113">
+      <c r="G11" s="76"/>
+      <c r="H11" s="57">
         <v>220</v>
       </c>
-      <c r="I11" s="110">
+      <c r="I11" s="56">
         <v>720</v>
       </c>
     </row>
@@ -1665,14 +1627,14 @@
       <c r="E12" s="43">
         <v>113</v>
       </c>
-      <c r="F12" s="114">
+      <c r="F12" s="75">
         <v>1200</v>
       </c>
-      <c r="G12" s="115"/>
-      <c r="H12" s="113">
+      <c r="G12" s="76"/>
+      <c r="H12" s="57">
         <v>678.6</v>
       </c>
-      <c r="I12" s="110">
+      <c r="I12" s="56">
         <v>1878.6</v>
       </c>
     </row>
@@ -1690,14 +1652,14 @@
       <c r="E13" s="44">
         <v>34</v>
       </c>
-      <c r="F13" s="111">
+      <c r="F13" s="73">
         <v>350</v>
       </c>
-      <c r="G13" s="112"/>
-      <c r="H13" s="113">
+      <c r="G13" s="74"/>
+      <c r="H13" s="57">
         <v>59.5</v>
       </c>
-      <c r="I13" s="110">
+      <c r="I13" s="56">
         <v>409.5</v>
       </c>
     </row>
@@ -1707,8 +1669,8 @@
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="30"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="68"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="78"/>
       <c r="H14" s="33"/>
       <c r="I14" s="41"/>
     </row>
@@ -1718,8 +1680,8 @@
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="31"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="58"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80"/>
       <c r="H15" s="32"/>
       <c r="I15" s="42"/>
     </row>
@@ -1729,8 +1691,8 @@
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
       <c r="E16" s="30"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="33"/>
       <c r="I16" s="41"/>
     </row>
@@ -1740,8 +1702,8 @@
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="58"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="80"/>
       <c r="H17" s="32"/>
       <c r="I17" s="42"/>
     </row>
@@ -1751,8 +1713,8 @@
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
       <c r="E18" s="30"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="33"/>
       <c r="I18" s="41"/>
     </row>
@@ -1762,8 +1724,8 @@
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="66"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="96"/>
       <c r="H19" s="11"/>
       <c r="I19" s="42"/>
     </row>
@@ -1773,8 +1735,8 @@
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="30"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="56"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="82"/>
       <c r="H20" s="33"/>
       <c r="I20" s="41"/>
     </row>
@@ -1784,8 +1746,8 @@
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="31"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="58"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="80"/>
       <c r="H21" s="32"/>
       <c r="I21" s="42"/>
     </row>
@@ -1795,8 +1757,8 @@
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
       <c r="E22" s="30"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="56"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="82"/>
       <c r="H22" s="33"/>
       <c r="I22" s="41"/>
     </row>
@@ -1806,8 +1768,8 @@
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="31"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="80"/>
       <c r="H23" s="32"/>
       <c r="I23" s="42"/>
     </row>
@@ -1817,8 +1779,8 @@
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="30"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="82"/>
       <c r="H24" s="33"/>
       <c r="I24" s="41"/>
     </row>
@@ -1828,8 +1790,8 @@
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="66"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="96"/>
       <c r="H25" s="11"/>
       <c r="I25" s="42"/>
     </row>
@@ -1839,8 +1801,8 @@
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="30"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="68"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="78"/>
       <c r="H26" s="33"/>
       <c r="I26" s="41"/>
     </row>
@@ -1850,8 +1812,8 @@
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="31"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="58"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="80"/>
       <c r="H27" s="32"/>
       <c r="I27" s="42"/>
     </row>
@@ -1861,8 +1823,8 @@
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="74"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="98"/>
       <c r="H28" s="10"/>
       <c r="I28" s="41"/>
     </row>
@@ -1872,8 +1834,8 @@
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="76"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="100"/>
       <c r="H29" s="11"/>
       <c r="I29" s="42"/>
     </row>
@@ -1883,8 +1845,8 @@
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="78"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="102"/>
       <c r="H30" s="10"/>
       <c r="I30" s="41"/>
     </row>
@@ -1894,8 +1856,8 @@
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="31"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="58"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="80"/>
       <c r="H31" s="32"/>
       <c r="I31" s="42"/>
     </row>
@@ -1905,8 +1867,8 @@
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="30"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="64"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="104"/>
       <c r="H32" s="33"/>
       <c r="I32" s="41"/>
     </row>
@@ -1916,8 +1878,8 @@
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="76"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="100"/>
       <c r="H33" s="11"/>
       <c r="I33" s="42"/>
     </row>
@@ -1927,8 +1889,8 @@
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="74"/>
+      <c r="F34" s="97"/>
+      <c r="G34" s="98"/>
       <c r="H34" s="10"/>
       <c r="I34" s="41"/>
     </row>
@@ -1938,8 +1900,8 @@
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="76"/>
+      <c r="F35" s="99"/>
+      <c r="G35" s="100"/>
       <c r="H35" s="11"/>
       <c r="I35" s="42"/>
     </row>
@@ -1949,8 +1911,8 @@
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="78"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="102"/>
       <c r="H36" s="10"/>
       <c r="I36" s="41"/>
     </row>
@@ -1960,8 +1922,8 @@
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="76"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="100"/>
       <c r="H37" s="11"/>
       <c r="I37" s="42"/>
     </row>
@@ -1971,8 +1933,8 @@
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="30"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="68"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="78"/>
       <c r="H38" s="33"/>
       <c r="I38" s="41"/>
     </row>
@@ -1982,8 +1944,8 @@
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="31"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="58"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="80"/>
       <c r="H39" s="32"/>
       <c r="I39" s="42"/>
     </row>
@@ -1993,8 +1955,8 @@
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
       <c r="E40" s="30"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="68"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="78"/>
       <c r="H40" s="33"/>
       <c r="I40" s="41"/>
     </row>
@@ -2004,8 +1966,8 @@
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
       <c r="E41" s="31"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="58"/>
+      <c r="F41" s="79"/>
+      <c r="G41" s="80"/>
       <c r="H41" s="32"/>
       <c r="I41" s="42"/>
     </row>
@@ -2015,8 +1977,8 @@
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
       <c r="E42" s="30"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="70"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="106"/>
       <c r="H42" s="33"/>
       <c r="I42" s="41"/>
     </row>
@@ -2026,8 +1988,8 @@
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="31"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="72"/>
+      <c r="F43" s="107"/>
+      <c r="G43" s="108"/>
       <c r="H43" s="32"/>
       <c r="I43" s="42"/>
     </row>
@@ -2037,8 +1999,8 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
       <c r="E44" s="30"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="56"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="82"/>
       <c r="H44" s="33"/>
       <c r="I44" s="41"/>
     </row>
@@ -2048,8 +2010,8 @@
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
       <c r="E45" s="31"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="60"/>
+      <c r="F45" s="109"/>
+      <c r="G45" s="110"/>
       <c r="H45" s="32"/>
       <c r="I45" s="42"/>
     </row>
@@ -2059,8 +2021,8 @@
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
       <c r="E46" s="30"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="70"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="106"/>
       <c r="H46" s="33"/>
       <c r="I46" s="41"/>
     </row>
@@ -2070,8 +2032,8 @@
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
       <c r="E47" s="31"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="72"/>
+      <c r="F47" s="107"/>
+      <c r="G47" s="108"/>
       <c r="H47" s="32"/>
       <c r="I47" s="42"/>
     </row>
@@ -2081,215 +2043,350 @@
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
       <c r="E48" s="30"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="56"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="82"/>
       <c r="H48" s="33"/>
       <c r="I48" s="41"/>
     </row>
-    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="47"/>
       <c r="B49" s="32"/>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
       <c r="E49" s="31"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="60"/>
+      <c r="F49" s="109"/>
+      <c r="G49" s="110"/>
       <c r="H49" s="32"/>
       <c r="I49" s="42"/>
     </row>
-    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="47"/>
       <c r="B50" s="33"/>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
       <c r="E50" s="30"/>
-      <c r="F50" s="63"/>
-      <c r="G50" s="64"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="104"/>
       <c r="H50" s="33"/>
       <c r="I50" s="41"/>
     </row>
-    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="47"/>
       <c r="B51" s="32"/>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="119"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="112"/>
       <c r="H51" s="11"/>
       <c r="I51" s="42"/>
     </row>
-    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="47"/>
       <c r="B52" s="33"/>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
       <c r="E52" s="30"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="64"/>
+      <c r="F52" s="103"/>
+      <c r="G52" s="104"/>
       <c r="H52" s="33"/>
       <c r="I52" s="41"/>
     </row>
-    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="47"/>
       <c r="B53" s="32"/>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="119"/>
+      <c r="F53" s="111"/>
+      <c r="G53" s="112"/>
       <c r="H53" s="11"/>
       <c r="I53" s="42"/>
     </row>
-    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="47"/>
       <c r="B54" s="33"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="30"/>
-      <c r="F54" s="63"/>
-      <c r="G54" s="64"/>
+      <c r="F54" s="103"/>
+      <c r="G54" s="104"/>
       <c r="H54" s="33"/>
       <c r="I54" s="41"/>
     </row>
-    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="47"/>
       <c r="B55" s="32"/>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="119"/>
+      <c r="F55" s="111"/>
+      <c r="G55" s="112"/>
       <c r="H55" s="11"/>
       <c r="I55" s="42"/>
     </row>
-    <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="47"/>
       <c r="B56" s="33"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="30"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="64"/>
+      <c r="F56" s="103"/>
+      <c r="G56" s="104"/>
       <c r="H56" s="33"/>
       <c r="I56" s="41"/>
     </row>
-    <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="47"/>
       <c r="B57" s="32"/>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
-      <c r="F57" s="118"/>
-      <c r="G57" s="119"/>
+      <c r="F57" s="111"/>
+      <c r="G57" s="112"/>
       <c r="H57" s="11"/>
       <c r="I57" s="42"/>
     </row>
-    <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="47"/>
       <c r="B58" s="33"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="30"/>
-      <c r="F58" s="67"/>
-      <c r="G58" s="68"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="78"/>
       <c r="H58" s="33"/>
       <c r="I58" s="41"/>
     </row>
-    <row r="59" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="47"/>
       <c r="B59" s="32"/>
       <c r="C59" s="11"/>
       <c r="D59" s="34"/>
       <c r="E59" s="31"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="58"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="80"/>
       <c r="H59" s="32"/>
       <c r="I59" s="42"/>
     </row>
-    <row r="60" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="47"/>
       <c r="B60" s="33"/>
       <c r="C60" s="30"/>
       <c r="D60" s="36"/>
       <c r="E60" s="38"/>
-      <c r="F60" s="55"/>
-      <c r="G60" s="56"/>
+      <c r="F60" s="81"/>
+      <c r="G60" s="82"/>
       <c r="H60" s="33"/>
       <c r="I60" s="41"/>
     </row>
-    <row r="61" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="47"/>
       <c r="B61" s="32"/>
       <c r="C61" s="31"/>
       <c r="D61" s="37"/>
       <c r="E61" s="39"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="58"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="80"/>
       <c r="H61" s="32"/>
       <c r="I61" s="42"/>
     </row>
-    <row r="62" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="47"/>
       <c r="B62" s="33"/>
       <c r="C62" s="10"/>
       <c r="D62" s="35"/>
       <c r="E62" s="30"/>
-      <c r="F62" s="55"/>
-      <c r="G62" s="56"/>
+      <c r="F62" s="81"/>
+      <c r="G62" s="82"/>
       <c r="H62" s="33"/>
       <c r="I62" s="41"/>
     </row>
-    <row r="63" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="47"/>
-      <c r="B63" s="50"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="60"/>
-      <c r="H63" s="50"/>
-      <c r="I63" s="53"/>
-    </row>
-    <row r="64" spans="1:10" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="32"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="79"/>
+      <c r="G63" s="80"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="42"/>
+    </row>
+    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="47"/>
-      <c r="B64" s="93" t="s">
+      <c r="B64" s="33"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="82"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="41"/>
+    </row>
+    <row r="65" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="47"/>
+      <c r="B65" s="32"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="79"/>
+      <c r="G65" s="80"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="42"/>
+    </row>
+    <row r="66" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="47"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="81"/>
+      <c r="G66" s="82"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="41"/>
+    </row>
+    <row r="67" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="47"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="79"/>
+      <c r="G67" s="80"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="42"/>
+    </row>
+    <row r="68" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="47"/>
+      <c r="B68" s="33"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="41"/>
+    </row>
+    <row r="69" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="47"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="79"/>
+      <c r="G69" s="80"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="42"/>
+    </row>
+    <row r="70" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="47"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="81"/>
+      <c r="G70" s="82"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="41"/>
+    </row>
+    <row r="71" spans="1:10" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="47"/>
+      <c r="B71" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="C64" s="94"/>
-      <c r="D64" s="94"/>
-      <c r="E64" s="95"/>
-      <c r="F64" s="61">
-        <f>SUM(F9:F63)</f>
+      <c r="C71" s="63"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="64"/>
+      <c r="F71" s="113">
+        <f>SUM(F9:F70)</f>
         <v>2260</v>
       </c>
-      <c r="G64" s="62"/>
-      <c r="H64" s="52">
-        <f>SUM(H9:H63)</f>
+      <c r="G71" s="114"/>
+      <c r="H71" s="50">
+        <f>SUM(H9:H70)</f>
         <v>1031.3</v>
       </c>
-      <c r="I64" s="54">
-        <f>SUM(I9:I63)</f>
+      <c r="I71" s="51">
+        <f>SUM(I9:I70)</f>
         <v>3291.3</v>
       </c>
-      <c r="J64" s="49"/>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B66" s="91" t="s">
+      <c r="J71" s="49"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B73" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="92"/>
-      <c r="G66" s="92"/>
-      <c r="H66" s="92"/>
-      <c r="I66" s="92"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="61"/>
+      <c r="E73" s="61"/>
+      <c r="F73" s="61"/>
+      <c r="G73" s="61"/>
+      <c r="H73" s="61"/>
+      <c r="I73" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="B64:E64"/>
+  <mergeCells count="74">
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="B71:E71"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="H4:I4"/>
@@ -2304,57 +2401,6 @@
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2377,15 +2423,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
@@ -2413,7 +2459,7 @@
       <c r="I4" s="13"/>
     </row>
     <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2422,22 +2468,22 @@
       <c r="D6" s="1">
         <v>218</v>
       </c>
-      <c r="E6" s="106" t="s">
+      <c r="E6" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="116">
+      <c r="F6" s="58">
         <v>30</v>
       </c>
-      <c r="G6" s="109">
+      <c r="G6" s="55">
         <v>32.700000000000003</v>
       </c>
-      <c r="H6" s="117">
+      <c r="H6" s="59">
         <f>F6+G6</f>
         <v>62.7</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="105" t="s">
+      <c r="B7" s="53" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2446,22 +2492,22 @@
       <c r="D7" s="9">
         <v>45</v>
       </c>
-      <c r="E7" s="106" t="s">
+      <c r="E7" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="116">
+      <c r="F7" s="58">
         <v>180</v>
       </c>
-      <c r="G7" s="109">
+      <c r="G7" s="55">
         <v>40.5</v>
       </c>
-      <c r="H7" s="117">
+      <c r="H7" s="59">
         <f>F7+G7</f>
         <v>220.5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="53" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2470,22 +2516,22 @@
       <c r="D8" s="2">
         <v>88</v>
       </c>
-      <c r="E8" s="106" t="s">
+      <c r="E8" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="116">
+      <c r="F8" s="58">
         <v>500</v>
       </c>
-      <c r="G8" s="109">
+      <c r="G8" s="55">
         <v>220</v>
       </c>
-      <c r="H8" s="117">
+      <c r="H8" s="59">
         <f>F8+G8</f>
         <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="53" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2494,24 +2540,24 @@
       <c r="D9" s="2">
         <v>113</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="116">
+      <c r="F9" s="58">
         <v>1200</v>
       </c>
-      <c r="G9" s="109">
+      <c r="G9" s="55">
         <v>678.6</v>
       </c>
-      <c r="H9" s="117">
+      <c r="H9" s="59">
         <f>F9+G9</f>
         <v>1878.6</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="16"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="8"/>
       <c r="F10" s="5"/>
       <c r="G10" s="6"/>
@@ -2519,8 +2565,8 @@
     </row>
     <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="16"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="8"/>
       <c r="F11" s="5"/>
       <c r="G11" s="6"/>
@@ -2528,8 +2574,8 @@
     </row>
     <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="16"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
       <c r="E12" s="8"/>
       <c r="F12" s="5"/>
       <c r="G12" s="6"/>
@@ -2537,8 +2583,8 @@
     </row>
     <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="16"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
       <c r="E13" s="8"/>
       <c r="F13" s="5"/>
       <c r="G13" s="6"/>
@@ -2546,8 +2592,8 @@
     </row>
     <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="16"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
       <c r="E14" s="8"/>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
@@ -2555,8 +2601,8 @@
     </row>
     <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="16"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="8"/>
       <c r="F15" s="5"/>
       <c r="G15" s="6"/>
@@ -2564,8 +2610,8 @@
     </row>
     <row r="16" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="16"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
       <c r="E16" s="8"/>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
@@ -2573,8 +2619,8 @@
     </row>
     <row r="17" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="16"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="8"/>
       <c r="F17" s="5"/>
       <c r="G17" s="6"/>
@@ -2582,8 +2628,8 @@
     </row>
     <row r="18" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="16"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
       <c r="E18" s="8"/>
       <c r="F18" s="5"/>
       <c r="G18" s="6"/>
@@ -2591,8 +2637,8 @@
     </row>
     <row r="19" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="16"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
       <c r="E19" s="8"/>
       <c r="F19" s="5"/>
       <c r="G19" s="6"/>
@@ -2600,8 +2646,8 @@
     </row>
     <row r="20" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="16"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
       <c r="E20" s="8"/>
       <c r="F20" s="5"/>
       <c r="G20" s="6"/>
@@ -2609,8 +2655,8 @@
     </row>
     <row r="21" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="16"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
       <c r="E21" s="8"/>
       <c r="F21" s="5"/>
       <c r="G21" s="6"/>
@@ -2618,8 +2664,8 @@
     </row>
     <row r="22" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="16"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
       <c r="E22" s="8"/>
       <c r="F22" s="5"/>
       <c r="G22" s="6"/>
@@ -2627,8 +2673,8 @@
     </row>
     <row r="23" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="16"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="8"/>
       <c r="F23" s="5"/>
       <c r="G23" s="6"/>
@@ -2636,8 +2682,8 @@
     </row>
     <row r="24" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="16"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="8"/>
       <c r="F24" s="5"/>
       <c r="G24" s="6"/>
@@ -2645,8 +2691,8 @@
     </row>
     <row r="25" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="16"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
       <c r="E25" s="8"/>
       <c r="F25" s="5"/>
       <c r="G25" s="6"/>
@@ -2654,8 +2700,8 @@
     </row>
     <row r="26" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="16"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
       <c r="E26" s="8"/>
       <c r="F26" s="5"/>
       <c r="G26" s="6"/>
@@ -2663,8 +2709,8 @@
     </row>
     <row r="27" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="16"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
       <c r="E27" s="8"/>
       <c r="F27" s="5"/>
       <c r="G27" s="6"/>
@@ -2672,8 +2718,8 @@
     </row>
     <row r="28" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="16"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
       <c r="E28" s="8"/>
       <c r="F28" s="5"/>
       <c r="G28" s="6"/>
@@ -2681,8 +2727,8 @@
     </row>
     <row r="29" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="16"/>
-      <c r="C29" s="104"/>
-      <c r="D29" s="104"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
       <c r="E29" s="8"/>
       <c r="F29" s="5"/>
       <c r="G29" s="6"/>
@@ -2690,8 +2736,8 @@
     </row>
     <row r="30" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="16"/>
-      <c r="C30" s="104"/>
-      <c r="D30" s="104"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="8"/>
       <c r="F30" s="5"/>
       <c r="G30" s="6"/>
@@ -2699,8 +2745,8 @@
     </row>
     <row r="31" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="16"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="104"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
       <c r="E31" s="8"/>
       <c r="F31" s="5"/>
       <c r="G31" s="6"/>
@@ -2708,8 +2754,8 @@
     </row>
     <row r="32" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="16"/>
-      <c r="C32" s="104"/>
-      <c r="D32" s="104"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="8"/>
       <c r="F32" s="5"/>
       <c r="G32" s="6"/>
@@ -2717,8 +2763,8 @@
     </row>
     <row r="33" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="16"/>
-      <c r="C33" s="104"/>
-      <c r="D33" s="104"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="8"/>
       <c r="F33" s="5"/>
       <c r="G33" s="6"/>
@@ -2726,8 +2772,8 @@
     </row>
     <row r="34" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="16"/>
-      <c r="C34" s="104"/>
-      <c r="D34" s="104"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="8"/>
       <c r="F34" s="5"/>
       <c r="G34" s="6"/>
@@ -2735,8 +2781,8 @@
     </row>
     <row r="35" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="16"/>
-      <c r="C35" s="104"/>
-      <c r="D35" s="104"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
       <c r="E35" s="8"/>
       <c r="F35" s="5"/>
       <c r="G35" s="6"/>
@@ -2744,8 +2790,8 @@
     </row>
     <row r="36" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="16"/>
-      <c r="C36" s="104"/>
-      <c r="D36" s="104"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
       <c r="E36" s="8"/>
       <c r="F36" s="5"/>
       <c r="G36" s="6"/>
@@ -2753,8 +2799,8 @@
     </row>
     <row r="37" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="16"/>
-      <c r="C37" s="104"/>
-      <c r="D37" s="104"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
       <c r="E37" s="8"/>
       <c r="F37" s="5"/>
       <c r="G37" s="6"/>
@@ -2762,8 +2808,8 @@
     </row>
     <row r="38" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="16"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="104"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
       <c r="E38" s="8"/>
       <c r="F38" s="5"/>
       <c r="G38" s="6"/>
@@ -2771,8 +2817,8 @@
     </row>
     <row r="39" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="16"/>
-      <c r="C39" s="104"/>
-      <c r="D39" s="104"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
       <c r="E39" s="8"/>
       <c r="F39" s="5"/>
       <c r="G39" s="6"/>
@@ -2780,8 +2826,8 @@
     </row>
     <row r="40" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="16"/>
-      <c r="C40" s="104"/>
-      <c r="D40" s="104"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
       <c r="E40" s="8"/>
       <c r="F40" s="5"/>
       <c r="G40" s="6"/>
@@ -2789,8 +2835,8 @@
     </row>
     <row r="41" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="16"/>
-      <c r="C41" s="104"/>
-      <c r="D41" s="104"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
       <c r="E41" s="8"/>
       <c r="F41" s="5"/>
       <c r="G41" s="6"/>
@@ -2798,8 +2844,8 @@
     </row>
     <row r="42" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="16"/>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
       <c r="E42" s="8"/>
       <c r="F42" s="5"/>
       <c r="G42" s="6"/>
@@ -2807,8 +2853,8 @@
     </row>
     <row r="43" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="16"/>
-      <c r="C43" s="104"/>
-      <c r="D43" s="104"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
       <c r="E43" s="8"/>
       <c r="F43" s="5"/>
       <c r="G43" s="6"/>
@@ -2816,8 +2862,8 @@
     </row>
     <row r="44" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="16"/>
-      <c r="C44" s="104"/>
-      <c r="D44" s="104"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
       <c r="E44" s="8"/>
       <c r="F44" s="5"/>
       <c r="G44" s="6"/>
@@ -2825,8 +2871,8 @@
     </row>
     <row r="45" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="16"/>
-      <c r="C45" s="104"/>
-      <c r="D45" s="104"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
       <c r="E45" s="8"/>
       <c r="F45" s="5"/>
       <c r="G45" s="6"/>
@@ -2834,8 +2880,8 @@
     </row>
     <row r="46" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="16"/>
-      <c r="C46" s="104"/>
-      <c r="D46" s="104"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
       <c r="E46" s="8"/>
       <c r="F46" s="5"/>
       <c r="G46" s="6"/>
@@ -2843,8 +2889,8 @@
     </row>
     <row r="47" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="16"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
       <c r="E47" s="8"/>
       <c r="F47" s="5"/>
       <c r="G47" s="6"/>
@@ -2852,8 +2898,8 @@
     </row>
     <row r="48" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="16"/>
-      <c r="C48" s="104"/>
-      <c r="D48" s="104"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
       <c r="E48" s="8"/>
       <c r="F48" s="5"/>
       <c r="G48" s="6"/>
@@ -2861,8 +2907,8 @@
     </row>
     <row r="49" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="16"/>
-      <c r="C49" s="104"/>
-      <c r="D49" s="104"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
       <c r="E49" s="8"/>
       <c r="F49" s="5"/>
       <c r="G49" s="6"/>
@@ -2870,8 +2916,8 @@
     </row>
     <row r="50" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="16"/>
-      <c r="C50" s="104"/>
-      <c r="D50" s="104"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
       <c r="E50" s="8"/>
       <c r="F50" s="5"/>
       <c r="G50" s="6"/>
@@ -2879,8 +2925,8 @@
     </row>
     <row r="51" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="16"/>
-      <c r="C51" s="104"/>
-      <c r="D51" s="104"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
       <c r="E51" s="8"/>
       <c r="F51" s="5"/>
       <c r="G51" s="6"/>
@@ -2888,8 +2934,8 @@
     </row>
     <row r="52" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="16"/>
-      <c r="C52" s="104"/>
-      <c r="D52" s="104"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
       <c r="E52" s="8"/>
       <c r="F52" s="5"/>
       <c r="G52" s="6"/>
@@ -2897,8 +2943,8 @@
     </row>
     <row r="53" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="16"/>
-      <c r="C53" s="104"/>
-      <c r="D53" s="104"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
       <c r="E53" s="8"/>
       <c r="F53" s="5"/>
       <c r="G53" s="6"/>
@@ -2906,8 +2952,8 @@
     </row>
     <row r="54" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="16"/>
-      <c r="C54" s="104"/>
-      <c r="D54" s="104"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="52"/>
       <c r="E54" s="8"/>
       <c r="F54" s="5"/>
       <c r="G54" s="6"/>
@@ -2915,8 +2961,8 @@
     </row>
     <row r="55" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="16"/>
-      <c r="C55" s="104"/>
-      <c r="D55" s="104"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
       <c r="E55" s="8"/>
       <c r="F55" s="5"/>
       <c r="G55" s="6"/>
@@ -2924,8 +2970,8 @@
     </row>
     <row r="56" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="16"/>
-      <c r="C56" s="104"/>
-      <c r="D56" s="104"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
       <c r="E56" s="8"/>
       <c r="F56" s="5"/>
       <c r="G56" s="6"/>
@@ -2933,8 +2979,8 @@
     </row>
     <row r="57" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="16"/>
-      <c r="C57" s="104"/>
-      <c r="D57" s="104"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="52"/>
       <c r="E57" s="8"/>
       <c r="F57" s="5"/>
       <c r="G57" s="6"/>
@@ -2965,12 +3011,12 @@
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="102" t="s">
+      <c r="B60" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="92"/>
-      <c r="D60" s="92"/>
-      <c r="E60" s="92"/>
+      <c r="C60" s="61"/>
+      <c r="D60" s="61"/>
+      <c r="E60" s="61"/>
       <c r="F60" s="12">
         <f>SUM(F6:F59)</f>
         <v>2260</v>
@@ -3006,13 +3052,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
     </row>
     <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
@@ -3196,10 +3242,10 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="92"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="12">
         <f>SUM(D6:D15)</f>
         <v>2260</v>

--- a/planilhas/relatorio_inadimplencia_modelo.xlsx
+++ b/planilhas/relatorio_inadimplencia_modelo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karol/Documents/Dashboard-Ativuz/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6473BFA0-BA61-5347-8BC4-E798191AE157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFEF528-7291-F94B-AF1E-34E90F2EB588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo Executivo" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,8 +286,50 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,11 +364,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E8449"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F3F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -395,8 +432,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EAF9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBDBD9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5F5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -827,12 +882,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -843,63 +909,58 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -911,28 +972,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -945,153 +990,26 @@
     <xf numFmtId="164" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="11" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1120,22 +1038,46 @@
     <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1144,6 +1086,117 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="21" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="21" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="21" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="21" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="21" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="23" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="10" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1151,6 +1204,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFD5F5E3"/>
+      <color rgb="FFFBDBD9"/>
+      <color rgb="FFD7EAF9"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1447,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="40.6640625" customWidth="1"/>
@@ -1461,82 +1521,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43"/>
+      <c r="A1" s="28"/>
     </row>
     <row r="2" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43"/>
-      <c r="B2" s="88" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43"/>
-      <c r="B3" s="90" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
     </row>
     <row r="4" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="43"/>
-      <c r="B4" s="25" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="105"/>
-      <c r="E4" s="92" t="s">
+      <c r="D4" s="45"/>
+      <c r="E4" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="93"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="107" t="s">
+      <c r="F4" s="56"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="108"/>
+      <c r="I4" s="48"/>
     </row>
     <row r="5" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="43"/>
-      <c r="B5" s="26">
-        <f>COUNTA(C9:C66)</f>
+      <c r="A5" s="28"/>
+      <c r="B5" s="23">
+        <f>COUNTA(C9:C104)</f>
         <v>5</v>
       </c>
-      <c r="C5" s="106">
-        <f>SUM(E9:E66)</f>
+      <c r="C5" s="46">
+        <f>SUM(E9:E104)</f>
         <v>498</v>
       </c>
-      <c r="D5" s="106"/>
-      <c r="E5" s="95">
-        <f>SUM(H9:H66)</f>
+      <c r="D5" s="46"/>
+      <c r="E5" s="58">
+        <f>SUM(H9:H104)</f>
         <v>1031.3</v>
       </c>
-      <c r="F5" s="96"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="109">
-        <f>SUM(I9:I66)</f>
+      <c r="F5" s="59"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="49">
+        <f>SUM(I9:I104)</f>
         <v>3291.3</v>
       </c>
-      <c r="I5" s="110"/>
+      <c r="I5" s="50"/>
     </row>
     <row r="6" spans="1:9" ht="10" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43"/>
+      <c r="A6" s="28"/>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="43"/>
-      <c r="B7" s="44" t="s">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1548,769 +1608,1239 @@
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="98" t="s">
+      <c r="F7" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="99"/>
+      <c r="G7" s="62"/>
       <c r="H7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="27" t="s">
+      <c r="I7" s="24" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="43"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="A8" s="28"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="43"/>
-      <c r="B9" s="41" t="s">
+      <c r="A9" s="28"/>
+      <c r="B9" s="67" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="1">
         <v>218</v>
       </c>
-      <c r="F9" s="111">
+      <c r="F9" s="82">
         <v>30</v>
       </c>
-      <c r="G9" s="112"/>
-      <c r="H9" s="51">
+      <c r="G9" s="83"/>
+      <c r="H9" s="36">
         <v>32.700000000000003</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="112">
         <v>62.7</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="43"/>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="67" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="27">
         <v>45</v>
       </c>
-      <c r="F10" s="113">
+      <c r="F10" s="80">
         <v>180</v>
       </c>
-      <c r="G10" s="114"/>
-      <c r="H10" s="53">
+      <c r="G10" s="81"/>
+      <c r="H10" s="37">
         <v>40.5</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="112">
         <v>220.5</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="43"/>
-      <c r="B11" s="41" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="67" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="26">
         <v>88</v>
       </c>
-      <c r="F11" s="115">
+      <c r="F11" s="84">
         <v>500</v>
       </c>
-      <c r="G11" s="116"/>
-      <c r="H11" s="53">
+      <c r="G11" s="85"/>
+      <c r="H11" s="37">
         <v>220</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="112">
         <v>720</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="43"/>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="67" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="26">
         <v>113</v>
       </c>
-      <c r="F12" s="115">
+      <c r="F12" s="84">
         <v>1200</v>
       </c>
-      <c r="G12" s="116"/>
-      <c r="H12" s="53">
+      <c r="G12" s="85"/>
+      <c r="H12" s="37">
         <v>678.6</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="112">
         <v>1878.6</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="43"/>
-      <c r="B13" s="41" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="67" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="27">
         <v>34</v>
       </c>
-      <c r="F13" s="113">
+      <c r="F13" s="80">
         <v>350</v>
       </c>
-      <c r="G13" s="114"/>
-      <c r="H13" s="53">
+      <c r="G13" s="81"/>
+      <c r="H13" s="108">
         <v>59.5</v>
       </c>
-      <c r="I13" s="52">
+      <c r="I13" s="111">
         <v>409.5</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="43"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="37"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="113"/>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="43"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="38"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="113"/>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="43"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="37"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="113"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="43"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="38"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="113"/>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="43"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="37"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="113"/>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="43"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="38"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="113"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="43"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="37"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="113"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="43"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="38"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="113"/>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="43"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="37"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="113"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="43"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="38"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="113"/>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="43"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="37"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="113"/>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="43"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="38"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="113"/>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="43"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="37"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="113"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="43"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="38"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="113"/>
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="43"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="37"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="113"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="43"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="38"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="113"/>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="43"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="37"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="113"/>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="43"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="38"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="113"/>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="43"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="37"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="69"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="113"/>
     </row>
     <row r="33" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="43"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="38"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="110"/>
+      <c r="I33" s="113"/>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="43"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="37"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="110"/>
+      <c r="I34" s="113"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="43"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="38"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="110"/>
+      <c r="I35" s="113"/>
     </row>
     <row r="36" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="43"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="84"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="37"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="94"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="110"/>
+      <c r="I36" s="113"/>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="43"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="73"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="38"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="93"/>
+      <c r="H37" s="110"/>
+      <c r="I37" s="113"/>
     </row>
     <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="43"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="37"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="86"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="113"/>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="43"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="38"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="89"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="113"/>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="43"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="37"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="86"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="109"/>
+      <c r="I40" s="113"/>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="43"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="38"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="109"/>
+      <c r="I41" s="113"/>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="43"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="37"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="99"/>
+      <c r="H42" s="109"/>
+      <c r="I42" s="113"/>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="43"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="79"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="38"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="87"/>
+      <c r="H43" s="109"/>
+      <c r="I43" s="113"/>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="43"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="63"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="37"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="88"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="109"/>
+      <c r="I44" s="113"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="43"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="38"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="97"/>
+      <c r="H45" s="109"/>
+      <c r="I45" s="113"/>
     </row>
     <row r="46" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="43"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="37"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="98"/>
+      <c r="G46" s="99"/>
+      <c r="H46" s="109"/>
+      <c r="I46" s="113"/>
     </row>
     <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="43"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="78"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="38"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="86"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="109"/>
+      <c r="I47" s="113"/>
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="43"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="63"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="37"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="109"/>
+      <c r="I48" s="113"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="43"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="38"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="97"/>
+      <c r="H49" s="109"/>
+      <c r="I49" s="113"/>
     </row>
     <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="43"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="71"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="37"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="69"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="97"/>
+      <c r="H50" s="109"/>
+      <c r="I50" s="113"/>
     </row>
     <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="43"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="72"/>
-      <c r="G51" s="73"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="38"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="92"/>
+      <c r="G51" s="93"/>
+      <c r="H51" s="110"/>
+      <c r="I51" s="113"/>
     </row>
     <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="43"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="37"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="68"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="96"/>
+      <c r="G52" s="97"/>
+      <c r="H52" s="109"/>
+      <c r="I52" s="113"/>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="43"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="73"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="38"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="88"/>
+      <c r="G53" s="89"/>
+      <c r="H53" s="109"/>
+      <c r="I53" s="113"/>
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="43"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="71"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="37"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="100"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="109"/>
+      <c r="I54" s="113"/>
     </row>
     <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="43"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="72"/>
-      <c r="G55" s="73"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="38"/>
+      <c r="A55" s="28"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="100"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="109"/>
+      <c r="I55" s="113"/>
     </row>
     <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="43"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="37"/>
+      <c r="A56" s="28"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="100"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="109"/>
+      <c r="I56" s="113"/>
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="43"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="75"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="38"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="100"/>
+      <c r="G57" s="101"/>
+      <c r="H57" s="109"/>
+      <c r="I57" s="113"/>
     </row>
     <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="43"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="62"/>
-      <c r="G58" s="63"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="37"/>
+      <c r="A58" s="28"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="69"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="70"/>
+      <c r="F58" s="100"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="109"/>
+      <c r="I58" s="113"/>
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="43"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="60"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="64"/>
-      <c r="G59" s="65"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="38"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="69"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="100"/>
+      <c r="G59" s="101"/>
+      <c r="H59" s="109"/>
+      <c r="I59" s="113"/>
     </row>
     <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="43"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="31"/>
-      <c r="I60" s="37"/>
+      <c r="A60" s="28"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="69"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="100"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="113"/>
     </row>
     <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="43"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="64"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="38"/>
+      <c r="A61" s="28"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="100"/>
+      <c r="G61" s="101"/>
+      <c r="H61" s="109"/>
+      <c r="I61" s="113"/>
     </row>
     <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="43"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="62"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="37"/>
+      <c r="A62" s="28"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="69"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="100"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="109"/>
+      <c r="I62" s="113"/>
     </row>
     <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="43"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="64"/>
-      <c r="G63" s="65"/>
-      <c r="H63" s="30"/>
-      <c r="I63" s="38"/>
+      <c r="A63" s="28"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="100"/>
+      <c r="G63" s="101"/>
+      <c r="H63" s="109"/>
+      <c r="I63" s="113"/>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="43"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="56"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="37"/>
-    </row>
-    <row r="65" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="43"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="64"/>
-      <c r="G65" s="65"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="38"/>
-    </row>
-    <row r="66" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="43"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="61"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="56"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="31"/>
-      <c r="I66" s="37"/>
-    </row>
-    <row r="67" spans="1:10" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="43"/>
-      <c r="B67" s="102" t="s">
+      <c r="A64" s="28"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="70"/>
+      <c r="F64" s="100"/>
+      <c r="G64" s="101"/>
+      <c r="H64" s="109"/>
+      <c r="I64" s="113"/>
+    </row>
+    <row r="65" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="28"/>
+      <c r="B65" s="68"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="70"/>
+      <c r="F65" s="100"/>
+      <c r="G65" s="101"/>
+      <c r="H65" s="109"/>
+      <c r="I65" s="113"/>
+    </row>
+    <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="28"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="71"/>
+      <c r="F66" s="102"/>
+      <c r="G66" s="103"/>
+      <c r="H66" s="109"/>
+      <c r="I66" s="113"/>
+    </row>
+    <row r="67" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="28"/>
+      <c r="B67" s="68"/>
+      <c r="C67" s="69"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="104"/>
+      <c r="G67" s="89"/>
+      <c r="H67" s="109"/>
+      <c r="I67" s="113"/>
+    </row>
+    <row r="68" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="28"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="102"/>
+      <c r="G68" s="103"/>
+      <c r="H68" s="109"/>
+      <c r="I68" s="113"/>
+    </row>
+    <row r="69" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="28"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="102"/>
+      <c r="G69" s="101"/>
+      <c r="H69" s="109"/>
+      <c r="I69" s="113"/>
+    </row>
+    <row r="70" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="28"/>
+      <c r="B70" s="68"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="71"/>
+      <c r="F70" s="102"/>
+      <c r="G70" s="101"/>
+      <c r="H70" s="109"/>
+      <c r="I70" s="113"/>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="28"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="69"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="71"/>
+      <c r="F71" s="102"/>
+      <c r="G71" s="101"/>
+      <c r="H71" s="109"/>
+      <c r="I71" s="113"/>
+    </row>
+    <row r="72" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="28"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="71"/>
+      <c r="F72" s="102"/>
+      <c r="G72" s="101"/>
+      <c r="H72" s="109"/>
+      <c r="I72" s="113"/>
+    </row>
+    <row r="73" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="28"/>
+      <c r="B73" s="68"/>
+      <c r="C73" s="69"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="71"/>
+      <c r="F73" s="102"/>
+      <c r="G73" s="101"/>
+      <c r="H73" s="109"/>
+      <c r="I73" s="113"/>
+    </row>
+    <row r="74" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="28"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="69"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="71"/>
+      <c r="F74" s="102"/>
+      <c r="G74" s="101"/>
+      <c r="H74" s="109"/>
+      <c r="I74" s="113"/>
+    </row>
+    <row r="75" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="28"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="69"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="71"/>
+      <c r="F75" s="102"/>
+      <c r="G75" s="101"/>
+      <c r="H75" s="109"/>
+      <c r="I75" s="113"/>
+    </row>
+    <row r="76" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="28"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="69"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="71"/>
+      <c r="F76" s="102"/>
+      <c r="G76" s="101"/>
+      <c r="H76" s="109"/>
+      <c r="I76" s="113"/>
+    </row>
+    <row r="77" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="28"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="69"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="71"/>
+      <c r="F77" s="102"/>
+      <c r="G77" s="101"/>
+      <c r="H77" s="109"/>
+      <c r="I77" s="113"/>
+    </row>
+    <row r="78" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="28"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="69"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="71"/>
+      <c r="F78" s="102"/>
+      <c r="G78" s="101"/>
+      <c r="H78" s="109"/>
+      <c r="I78" s="113"/>
+    </row>
+    <row r="79" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="28"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="69"/>
+      <c r="D79" s="69"/>
+      <c r="E79" s="71"/>
+      <c r="F79" s="102"/>
+      <c r="G79" s="101"/>
+      <c r="H79" s="109"/>
+      <c r="I79" s="113"/>
+    </row>
+    <row r="80" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="28"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="102"/>
+      <c r="G80" s="101"/>
+      <c r="H80" s="109"/>
+      <c r="I80" s="113"/>
+    </row>
+    <row r="81" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="28"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="71"/>
+      <c r="F81" s="102"/>
+      <c r="G81" s="101"/>
+      <c r="H81" s="109"/>
+      <c r="I81" s="113"/>
+    </row>
+    <row r="82" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="28"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="71"/>
+      <c r="F82" s="102"/>
+      <c r="G82" s="101"/>
+      <c r="H82" s="109"/>
+      <c r="I82" s="113"/>
+    </row>
+    <row r="83" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="28"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="69"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="71"/>
+      <c r="F83" s="102"/>
+      <c r="G83" s="101"/>
+      <c r="H83" s="109"/>
+      <c r="I83" s="113"/>
+    </row>
+    <row r="84" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="28"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="69"/>
+      <c r="D84" s="69"/>
+      <c r="E84" s="71"/>
+      <c r="F84" s="102"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="109"/>
+      <c r="I84" s="113"/>
+    </row>
+    <row r="85" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="28"/>
+      <c r="B85" s="68"/>
+      <c r="C85" s="69"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="71"/>
+      <c r="F85" s="102"/>
+      <c r="G85" s="101"/>
+      <c r="H85" s="109"/>
+      <c r="I85" s="113"/>
+    </row>
+    <row r="86" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="28"/>
+      <c r="B86" s="68"/>
+      <c r="C86" s="69"/>
+      <c r="D86" s="69"/>
+      <c r="E86" s="71"/>
+      <c r="F86" s="102"/>
+      <c r="G86" s="101"/>
+      <c r="H86" s="109"/>
+      <c r="I86" s="113"/>
+    </row>
+    <row r="87" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="28"/>
+      <c r="B87" s="68"/>
+      <c r="C87" s="69"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="71"/>
+      <c r="F87" s="102"/>
+      <c r="G87" s="101"/>
+      <c r="H87" s="109"/>
+      <c r="I87" s="113"/>
+    </row>
+    <row r="88" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="28"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="69"/>
+      <c r="D88" s="69"/>
+      <c r="E88" s="71"/>
+      <c r="F88" s="102"/>
+      <c r="G88" s="101"/>
+      <c r="H88" s="109"/>
+      <c r="I88" s="113"/>
+    </row>
+    <row r="89" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="28"/>
+      <c r="B89" s="68"/>
+      <c r="C89" s="69"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="71"/>
+      <c r="F89" s="102"/>
+      <c r="G89" s="101"/>
+      <c r="H89" s="109"/>
+      <c r="I89" s="113"/>
+    </row>
+    <row r="90" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="28"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="69"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="71"/>
+      <c r="F90" s="102"/>
+      <c r="G90" s="101"/>
+      <c r="H90" s="109"/>
+      <c r="I90" s="113"/>
+    </row>
+    <row r="91" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="28"/>
+      <c r="B91" s="68"/>
+      <c r="C91" s="69"/>
+      <c r="D91" s="69"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="102"/>
+      <c r="G91" s="101"/>
+      <c r="H91" s="109"/>
+      <c r="I91" s="113"/>
+    </row>
+    <row r="92" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="28"/>
+      <c r="B92" s="68"/>
+      <c r="C92" s="69"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="71"/>
+      <c r="F92" s="102"/>
+      <c r="G92" s="101"/>
+      <c r="H92" s="109"/>
+      <c r="I92" s="113"/>
+    </row>
+    <row r="93" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="28"/>
+      <c r="B93" s="68"/>
+      <c r="C93" s="69"/>
+      <c r="D93" s="69"/>
+      <c r="E93" s="69"/>
+      <c r="F93" s="92"/>
+      <c r="G93" s="93"/>
+      <c r="H93" s="110"/>
+      <c r="I93" s="113"/>
+    </row>
+    <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="28"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="69"/>
+      <c r="D94" s="69"/>
+      <c r="E94" s="70"/>
+      <c r="F94" s="96"/>
+      <c r="G94" s="97"/>
+      <c r="H94" s="109"/>
+      <c r="I94" s="113"/>
+    </row>
+    <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="28"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="69"/>
+      <c r="D95" s="69"/>
+      <c r="E95" s="69"/>
+      <c r="F95" s="105"/>
+      <c r="G95" s="106"/>
+      <c r="H95" s="110"/>
+      <c r="I95" s="113"/>
+    </row>
+    <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="28"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="69"/>
+      <c r="D96" s="73"/>
+      <c r="E96" s="70"/>
+      <c r="F96" s="88"/>
+      <c r="G96" s="89"/>
+      <c r="H96" s="109"/>
+      <c r="I96" s="113"/>
+    </row>
+    <row r="97" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="28"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="70"/>
+      <c r="D97" s="74"/>
+      <c r="E97" s="75"/>
+      <c r="F97" s="88"/>
+      <c r="G97" s="89"/>
+      <c r="H97" s="109"/>
+      <c r="I97" s="113"/>
+    </row>
+    <row r="98" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="28"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="76"/>
+      <c r="E98" s="75"/>
+      <c r="F98" s="88"/>
+      <c r="G98" s="89"/>
+      <c r="H98" s="109"/>
+      <c r="I98" s="113"/>
+    </row>
+    <row r="99" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="28"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="70"/>
+      <c r="D99" s="77"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="88"/>
+      <c r="G99" s="89"/>
+      <c r="H99" s="109"/>
+      <c r="I99" s="113"/>
+    </row>
+    <row r="100" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="28"/>
+      <c r="B100" s="68"/>
+      <c r="C100" s="70"/>
+      <c r="D100" s="78"/>
+      <c r="E100" s="75"/>
+      <c r="F100" s="88"/>
+      <c r="G100" s="89"/>
+      <c r="H100" s="109"/>
+      <c r="I100" s="113"/>
+    </row>
+    <row r="101" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="28"/>
+      <c r="B101" s="68"/>
+      <c r="C101" s="70"/>
+      <c r="D101" s="77"/>
+      <c r="E101" s="75"/>
+      <c r="F101" s="88"/>
+      <c r="G101" s="89"/>
+      <c r="H101" s="109"/>
+      <c r="I101" s="113"/>
+    </row>
+    <row r="102" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="28"/>
+      <c r="B102" s="68"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="79"/>
+      <c r="E102" s="75"/>
+      <c r="F102" s="107"/>
+      <c r="G102" s="103"/>
+      <c r="H102" s="109"/>
+      <c r="I102" s="113"/>
+    </row>
+    <row r="103" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="28"/>
+      <c r="B103" s="68"/>
+      <c r="C103" s="71"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="88"/>
+      <c r="G103" s="89"/>
+      <c r="H103" s="109"/>
+      <c r="I103" s="113"/>
+    </row>
+    <row r="104" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="28"/>
+      <c r="B104" s="68"/>
+      <c r="C104" s="71"/>
+      <c r="D104" s="79"/>
+      <c r="E104" s="75"/>
+      <c r="F104" s="107"/>
+      <c r="G104" s="103"/>
+      <c r="H104" s="109"/>
+      <c r="I104" s="113"/>
+    </row>
+    <row r="105" spans="1:10" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="28"/>
+      <c r="B105" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C67" s="103"/>
-      <c r="D67" s="103"/>
-      <c r="E67" s="104"/>
-      <c r="F67" s="66">
-        <f>SUM(F9:F66)</f>
+      <c r="C105" s="43"/>
+      <c r="D105" s="43"/>
+      <c r="E105" s="44"/>
+      <c r="F105" s="63">
+        <f>SUM(F9:F104)</f>
         <v>2260</v>
       </c>
-      <c r="G67" s="67"/>
-      <c r="H67" s="46">
-        <f>SUM(H9:H66)</f>
+      <c r="G105" s="64"/>
+      <c r="H105" s="31">
+        <f>SUM(H9:H104)</f>
         <v>1031.3</v>
       </c>
-      <c r="I67" s="47">
-        <f>SUM(I9:I66)</f>
+      <c r="I105" s="32">
+        <f>SUM(I9:I104)</f>
         <v>3291.3</v>
       </c>
-      <c r="J67" s="45"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B69" s="100" t="s">
+      <c r="J105" s="30"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B107" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C69" s="101"/>
-      <c r="D69" s="101"/>
-      <c r="E69" s="101"/>
-      <c r="F69" s="101"/>
-      <c r="G69" s="101"/>
-      <c r="H69" s="101"/>
-      <c r="I69" s="101"/>
+      <c r="C107" s="41"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="41"/>
+      <c r="F107" s="41"/>
+      <c r="G107" s="41"/>
+      <c r="H107" s="41"/>
+      <c r="I107" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B107:I107"/>
+    <mergeCell ref="B105:E105"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="H4:I4"/>
@@ -2325,58 +2855,6 @@
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F65:G65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2385,7 +2863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:I75"/>
+  <dimension ref="A2:I126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2399,43 +2877,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="13"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="34" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2444,46 +2922,46 @@
       <c r="D6" s="1">
         <v>218</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="38">
         <v>30</v>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="36">
         <v>32.700000000000003</v>
       </c>
-      <c r="H6" s="55">
+      <c r="H6" s="39">
         <f>F6+G6</f>
         <v>62.7</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="34" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>45</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="38">
         <v>180</v>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="36">
         <v>40.5</v>
       </c>
-      <c r="H7" s="55">
+      <c r="H7" s="39">
         <f>F7+G7</f>
         <v>220.5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="34" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2492,22 +2970,22 @@
       <c r="D8" s="2">
         <v>88</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="38">
         <v>500</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="36">
         <v>220</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="39">
         <f>F8+G8</f>
         <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2516,619 +2994,1078 @@
       <c r="D9" s="2">
         <v>113</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="38">
         <v>1200</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="36">
         <v>678.6</v>
       </c>
-      <c r="H9" s="55">
+      <c r="H9" s="39">
         <f>F9+G9</f>
         <v>1878.6</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="14"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="14"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="7"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="14"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="7"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="14"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="7"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="14"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="7"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="14"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="7"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="14"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="7"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="14"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="7"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="14"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="7"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="14"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="7"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="14"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="7"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="14"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="7"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="14"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="7"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="14"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="7"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6"/>
     </row>
     <row r="24" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="14"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="7"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="14"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="7"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="14"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="7"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="14"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="7"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="14"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="7"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="14"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="7"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="14"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="7"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="14"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="7"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="14"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="7"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="14"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="7"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="14"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="7"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="14"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="7"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="14"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="7"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="14"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="7"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="14"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="7"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="6"/>
     </row>
     <row r="39" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="14"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="7"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="6"/>
     </row>
     <row r="40" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="14"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="7"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="6"/>
     </row>
     <row r="41" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="14"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="7"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="6"/>
     </row>
     <row r="42" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="14"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="7"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="14"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="7"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="14"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="7"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="14"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="7"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
     </row>
     <row r="46" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="14"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="7"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
     </row>
     <row r="47" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="14"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="7"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="14"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="7"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
     </row>
     <row r="49" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="14"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="7"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
     </row>
     <row r="50" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="14"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="7"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="6"/>
     </row>
     <row r="51" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="14"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="7"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="14"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="7"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="6"/>
     </row>
     <row r="53" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="14"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="7"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="6"/>
     </row>
     <row r="54" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="14"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="7"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="6"/>
     </row>
     <row r="55" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="14"/>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="7"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="6"/>
     </row>
     <row r="56" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="14"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="7"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="6"/>
     </row>
     <row r="57" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="14"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="7"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="6"/>
     </row>
     <row r="58" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="14"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="7"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="6"/>
     </row>
     <row r="59" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="14"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="7"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="6"/>
     </row>
     <row r="60" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="14"/>
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="7"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="6"/>
     </row>
     <row r="61" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="14"/>
-      <c r="C61" s="48"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="7"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="6"/>
     </row>
     <row r="62" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="14"/>
-      <c r="C62" s="48"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="7"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="6"/>
     </row>
     <row r="63" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="14"/>
-      <c r="C63" s="48"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="7"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="6"/>
     </row>
     <row r="64" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="14"/>
-      <c r="C64" s="48"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="7"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="6"/>
     </row>
     <row r="65" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="14"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="7"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="6"/>
     </row>
     <row r="66" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="14"/>
-      <c r="C66" s="48"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="7"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="6"/>
     </row>
     <row r="67" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="14"/>
-      <c r="C67" s="48"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="7"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="33"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="6"/>
     </row>
     <row r="68" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="14"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="7"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="6"/>
     </row>
     <row r="69" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="14"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="7"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="6"/>
     </row>
     <row r="70" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="14"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="7"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="6"/>
     </row>
     <row r="71" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="14"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="7"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="6"/>
     </row>
     <row r="72" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="14"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="7"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="33"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="6"/>
     </row>
     <row r="73" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="14"/>
-      <c r="C73" s="48"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="7"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B75" s="117" t="s">
+      <c r="B73" s="11"/>
+      <c r="C73" s="33"/>
+      <c r="D73" s="33"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="6"/>
+    </row>
+    <row r="74" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="11"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="33"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="6"/>
+    </row>
+    <row r="75" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="11"/>
+      <c r="C75" s="33"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="6"/>
+    </row>
+    <row r="76" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="11"/>
+      <c r="C76" s="33"/>
+      <c r="D76" s="33"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="6"/>
+    </row>
+    <row r="77" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="11"/>
+      <c r="C77" s="33"/>
+      <c r="D77" s="33"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="6"/>
+    </row>
+    <row r="78" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="11"/>
+      <c r="C78" s="33"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="6"/>
+    </row>
+    <row r="79" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="11"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="33"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="6"/>
+    </row>
+    <row r="80" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="11"/>
+      <c r="C80" s="33"/>
+      <c r="D80" s="33"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="6"/>
+    </row>
+    <row r="81" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="11"/>
+      <c r="C81" s="33"/>
+      <c r="D81" s="33"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="6"/>
+    </row>
+    <row r="82" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="11"/>
+      <c r="C82" s="33"/>
+      <c r="D82" s="33"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="6"/>
+    </row>
+    <row r="83" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="11"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="6"/>
+    </row>
+    <row r="84" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="11"/>
+      <c r="C84" s="33"/>
+      <c r="D84" s="33"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="6"/>
+    </row>
+    <row r="85" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="11"/>
+      <c r="C85" s="33"/>
+      <c r="D85" s="33"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="6"/>
+    </row>
+    <row r="86" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="11"/>
+      <c r="C86" s="33"/>
+      <c r="D86" s="33"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="6"/>
+    </row>
+    <row r="87" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="11"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="6"/>
+    </row>
+    <row r="88" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="11"/>
+      <c r="C88" s="33"/>
+      <c r="D88" s="33"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="6"/>
+    </row>
+    <row r="89" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="11"/>
+      <c r="C89" s="33"/>
+      <c r="D89" s="33"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="6"/>
+    </row>
+    <row r="90" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="11"/>
+      <c r="C90" s="33"/>
+      <c r="D90" s="33"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="6"/>
+    </row>
+    <row r="91" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="11"/>
+      <c r="C91" s="33"/>
+      <c r="D91" s="33"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="6"/>
+    </row>
+    <row r="92" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="11"/>
+      <c r="C92" s="33"/>
+      <c r="D92" s="33"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="6"/>
+    </row>
+    <row r="93" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="11"/>
+      <c r="C93" s="33"/>
+      <c r="D93" s="33"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="6"/>
+    </row>
+    <row r="94" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="11"/>
+      <c r="C94" s="33"/>
+      <c r="D94" s="33"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="6"/>
+    </row>
+    <row r="95" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="11"/>
+      <c r="C95" s="33"/>
+      <c r="D95" s="33"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="6"/>
+    </row>
+    <row r="96" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="11"/>
+      <c r="C96" s="33"/>
+      <c r="D96" s="33"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="6"/>
+    </row>
+    <row r="97" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="11"/>
+      <c r="C97" s="33"/>
+      <c r="D97" s="33"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="6"/>
+    </row>
+    <row r="98" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="11"/>
+      <c r="C98" s="33"/>
+      <c r="D98" s="33"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="6"/>
+    </row>
+    <row r="99" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="11"/>
+      <c r="C99" s="33"/>
+      <c r="D99" s="33"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="6"/>
+    </row>
+    <row r="100" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="11"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="33"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="6"/>
+    </row>
+    <row r="101" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B101" s="11"/>
+      <c r="C101" s="33"/>
+      <c r="D101" s="33"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="6"/>
+    </row>
+    <row r="102" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="11"/>
+      <c r="C102" s="33"/>
+      <c r="D102" s="33"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="6"/>
+    </row>
+    <row r="103" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="11"/>
+      <c r="C103" s="33"/>
+      <c r="D103" s="33"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="6"/>
+    </row>
+    <row r="104" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="11"/>
+      <c r="C104" s="33"/>
+      <c r="D104" s="33"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="6"/>
+    </row>
+    <row r="105" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="11"/>
+      <c r="C105" s="33"/>
+      <c r="D105" s="33"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="6"/>
+    </row>
+    <row r="106" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="11"/>
+      <c r="C106" s="33"/>
+      <c r="D106" s="33"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="6"/>
+    </row>
+    <row r="107" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="11"/>
+      <c r="C107" s="33"/>
+      <c r="D107" s="33"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="6"/>
+    </row>
+    <row r="108" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="11"/>
+      <c r="C108" s="33"/>
+      <c r="D108" s="33"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="6"/>
+    </row>
+    <row r="109" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="11"/>
+      <c r="C109" s="33"/>
+      <c r="D109" s="33"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="6"/>
+    </row>
+    <row r="110" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B110" s="11"/>
+      <c r="C110" s="33"/>
+      <c r="D110" s="33"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="6"/>
+    </row>
+    <row r="111" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="11"/>
+      <c r="C111" s="33"/>
+      <c r="D111" s="33"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="6"/>
+    </row>
+    <row r="112" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="11"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="6"/>
+    </row>
+    <row r="113" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="11"/>
+      <c r="C113" s="33"/>
+      <c r="D113" s="33"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="6"/>
+    </row>
+    <row r="114" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="11"/>
+      <c r="C114" s="33"/>
+      <c r="D114" s="33"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="6"/>
+    </row>
+    <row r="115" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="11"/>
+      <c r="C115" s="33"/>
+      <c r="D115" s="33"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="6"/>
+    </row>
+    <row r="116" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B116" s="11"/>
+      <c r="C116" s="33"/>
+      <c r="D116" s="33"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="6"/>
+    </row>
+    <row r="117" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="11"/>
+      <c r="C117" s="33"/>
+      <c r="D117" s="33"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="6"/>
+    </row>
+    <row r="118" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="11"/>
+      <c r="C118" s="33"/>
+      <c r="D118" s="33"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="6"/>
+    </row>
+    <row r="119" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="11"/>
+      <c r="C119" s="33"/>
+      <c r="D119" s="33"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="6"/>
+    </row>
+    <row r="120" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="11"/>
+      <c r="C120" s="33"/>
+      <c r="D120" s="33"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="6"/>
+    </row>
+    <row r="121" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="11"/>
+      <c r="C121" s="33"/>
+      <c r="D121" s="33"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="6"/>
+    </row>
+    <row r="122" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B122" s="11"/>
+      <c r="C122" s="33"/>
+      <c r="D122" s="33"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="6"/>
+    </row>
+    <row r="123" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="11"/>
+      <c r="C123" s="33"/>
+      <c r="D123" s="33"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="6"/>
+    </row>
+    <row r="124" spans="2:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="11"/>
+      <c r="C124" s="33"/>
+      <c r="D124" s="33"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="6"/>
+    </row>
+    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B126" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="101"/>
-      <c r="D75" s="101"/>
-      <c r="E75" s="101"/>
-      <c r="F75" s="12">
-        <f>SUM(F6:F74)</f>
+      <c r="C126" s="41"/>
+      <c r="D126" s="41"/>
+      <c r="E126" s="41"/>
+      <c r="F126" s="9">
+        <f>SUM(F6:F125)</f>
         <v>1910</v>
       </c>
-      <c r="G75" s="12">
-        <f>SUM(G6:G74)</f>
+      <c r="G126" s="9">
+        <f>SUM(G6:G125)</f>
         <v>971.8</v>
       </c>
-      <c r="H75" s="12">
-        <f>SUM(H6:H74)</f>
+      <c r="H126" s="9">
+        <f>SUM(H6:H125)</f>
         <v>2881.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B126:E126"/>
     <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3148,209 +4085,209 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="6" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="13">
         <v>0</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>0</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <f t="shared" ref="F6:F14" si="0">D6+E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="13">
         <v>0</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>0</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>0</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="13">
         <v>0</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>0</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="13">
         <v>0</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>0</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>0</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="13">
         <v>0</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>0</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>350</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>59.5</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
         <v>409.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="13">
         <v>1</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>1200</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>678.6</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>1878.6</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="13">
         <v>1</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>500</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>220</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="13">
         <v>3</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>210</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>73.2</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>283.2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="101"/>
-      <c r="D16" s="12">
+      <c r="C16" s="41"/>
+      <c r="D16" s="9">
         <f>SUM(D6:D15)</f>
         <v>2260</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="9">
         <f>SUM(E6:E15)</f>
         <v>1031.3</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="9">
         <f>SUM(F6:F15)</f>
         <v>3291.2999999999997</v>
       </c>

--- a/planilhas/relatorio_inadimplencia_modelo.xlsx
+++ b/planilhas/relatorio_inadimplencia_modelo.xlsx
@@ -306,7 +306,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -909,12 +909,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1293,6 +1313,32 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="21" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="21" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1592,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="40.6640625" customWidth="1" style="41" min="2" max="2"/>
@@ -1655,16 +1701,16 @@
         <v/>
       </c>
       <c r="C5" s="46">
-        <f>SUM(F9:F104)</f>
+        <f>SUM(F9:F200)</f>
         <v/>
       </c>
       <c r="E5" s="116">
-        <f>SUM(H9:H104)</f>
+        <f>SUM(H9:H200)</f>
         <v/>
       </c>
       <c r="G5" s="115" t="n"/>
       <c r="H5" s="49">
-        <f>SUM(I9:I104)</f>
+        <f>SUM(I9:I200)</f>
         <v/>
       </c>
     </row>
@@ -2588,392 +2634,1460 @@
     </row>
     <row r="79" ht="18" customHeight="1" s="41">
       <c r="A79" s="28" t="n"/>
-      <c r="B79" s="68" t="n"/>
-      <c r="C79" s="69" t="n"/>
-      <c r="D79" s="69" t="n"/>
-      <c r="E79" s="72" t="n"/>
-      <c r="F79" s="102" t="n"/>
-      <c r="G79" s="101" t="n"/>
-      <c r="H79" s="109" t="n"/>
-      <c r="I79" s="113" t="n"/>
+      <c r="B79" s="67" t="n"/>
+      <c r="C79" s="1" t="n"/>
+      <c r="D79" s="35" t="n"/>
+      <c r="E79" s="1" t="n"/>
+      <c r="F79" s="148" t="n"/>
+      <c r="G79" s="133" t="n"/>
+      <c r="H79" s="149" t="n"/>
+      <c r="I79" s="150" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1" s="41">
       <c r="A80" s="28" t="n"/>
-      <c r="B80" s="68" t="n"/>
-      <c r="C80" s="69" t="n"/>
-      <c r="D80" s="69" t="n"/>
-      <c r="E80" s="72" t="n"/>
-      <c r="F80" s="102" t="n"/>
-      <c r="G80" s="101" t="n"/>
-      <c r="H80" s="109" t="n"/>
-      <c r="I80" s="113" t="n"/>
+      <c r="B80" s="67" t="n"/>
+      <c r="C80" s="1" t="n"/>
+      <c r="D80" s="35" t="n"/>
+      <c r="E80" s="27" t="n"/>
+      <c r="F80" s="151" t="n"/>
+      <c r="G80" s="123" t="n"/>
+      <c r="H80" s="152" t="n"/>
+      <c r="I80" s="150" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1" s="41">
       <c r="A81" s="28" t="n"/>
-      <c r="B81" s="68" t="n"/>
-      <c r="C81" s="69" t="n"/>
-      <c r="D81" s="69" t="n"/>
-      <c r="E81" s="72" t="n"/>
-      <c r="F81" s="102" t="n"/>
-      <c r="G81" s="101" t="n"/>
-      <c r="H81" s="109" t="n"/>
-      <c r="I81" s="113" t="n"/>
+      <c r="B81" s="67" t="n"/>
+      <c r="C81" s="1" t="n"/>
+      <c r="D81" s="35" t="n"/>
+      <c r="E81" s="1" t="n"/>
+      <c r="F81" s="148" t="n"/>
+      <c r="G81" s="133" t="n"/>
+      <c r="H81" s="149" t="n"/>
+      <c r="I81" s="150" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1" s="41">
       <c r="A82" s="28" t="n"/>
-      <c r="B82" s="68" t="n"/>
-      <c r="C82" s="69" t="n"/>
-      <c r="D82" s="69" t="n"/>
-      <c r="E82" s="72" t="n"/>
-      <c r="F82" s="102" t="n"/>
-      <c r="G82" s="101" t="n"/>
-      <c r="H82" s="109" t="n"/>
-      <c r="I82" s="113" t="n"/>
+      <c r="B82" s="67" t="n"/>
+      <c r="C82" s="1" t="n"/>
+      <c r="D82" s="35" t="n"/>
+      <c r="E82" s="27" t="n"/>
+      <c r="F82" s="151" t="n"/>
+      <c r="G82" s="123" t="n"/>
+      <c r="H82" s="152" t="n"/>
+      <c r="I82" s="150" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1" s="41">
       <c r="A83" s="28" t="n"/>
-      <c r="B83" s="68" t="n"/>
-      <c r="C83" s="69" t="n"/>
-      <c r="D83" s="69" t="n"/>
-      <c r="E83" s="72" t="n"/>
-      <c r="F83" s="102" t="n"/>
-      <c r="G83" s="101" t="n"/>
-      <c r="H83" s="109" t="n"/>
-      <c r="I83" s="113" t="n"/>
+      <c r="B83" s="67" t="n"/>
+      <c r="C83" s="1" t="n"/>
+      <c r="D83" s="35" t="n"/>
+      <c r="E83" s="1" t="n"/>
+      <c r="F83" s="148" t="n"/>
+      <c r="G83" s="133" t="n"/>
+      <c r="H83" s="149" t="n"/>
+      <c r="I83" s="150" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1" s="41">
       <c r="A84" s="28" t="n"/>
-      <c r="B84" s="68" t="n"/>
-      <c r="C84" s="69" t="n"/>
-      <c r="D84" s="69" t="n"/>
-      <c r="E84" s="72" t="n"/>
-      <c r="F84" s="102" t="n"/>
-      <c r="G84" s="101" t="n"/>
-      <c r="H84" s="109" t="n"/>
-      <c r="I84" s="113" t="n"/>
+      <c r="B84" s="67" t="n"/>
+      <c r="C84" s="1" t="n"/>
+      <c r="D84" s="35" t="n"/>
+      <c r="E84" s="27" t="n"/>
+      <c r="F84" s="151" t="n"/>
+      <c r="G84" s="123" t="n"/>
+      <c r="H84" s="152" t="n"/>
+      <c r="I84" s="150" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1" s="41">
       <c r="A85" s="28" t="n"/>
-      <c r="B85" s="68" t="n"/>
-      <c r="C85" s="69" t="n"/>
-      <c r="D85" s="69" t="n"/>
-      <c r="E85" s="72" t="n"/>
-      <c r="F85" s="102" t="n"/>
-      <c r="G85" s="101" t="n"/>
-      <c r="H85" s="109" t="n"/>
-      <c r="I85" s="113" t="n"/>
+      <c r="B85" s="67" t="n"/>
+      <c r="C85" s="1" t="n"/>
+      <c r="D85" s="35" t="n"/>
+      <c r="E85" s="1" t="n"/>
+      <c r="F85" s="148" t="n"/>
+      <c r="G85" s="133" t="n"/>
+      <c r="H85" s="149" t="n"/>
+      <c r="I85" s="150" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1" s="41">
       <c r="A86" s="28" t="n"/>
-      <c r="B86" s="68" t="n"/>
-      <c r="C86" s="69" t="n"/>
-      <c r="D86" s="69" t="n"/>
-      <c r="E86" s="72" t="n"/>
-      <c r="F86" s="102" t="n"/>
-      <c r="G86" s="101" t="n"/>
-      <c r="H86" s="109" t="n"/>
-      <c r="I86" s="113" t="n"/>
+      <c r="B86" s="67" t="n"/>
+      <c r="C86" s="1" t="n"/>
+      <c r="D86" s="35" t="n"/>
+      <c r="E86" s="27" t="n"/>
+      <c r="F86" s="151" t="n"/>
+      <c r="G86" s="123" t="n"/>
+      <c r="H86" s="152" t="n"/>
+      <c r="I86" s="150" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1" s="41">
       <c r="A87" s="28" t="n"/>
-      <c r="B87" s="68" t="n"/>
-      <c r="C87" s="69" t="n"/>
-      <c r="D87" s="69" t="n"/>
-      <c r="E87" s="72" t="n"/>
-      <c r="F87" s="102" t="n"/>
-      <c r="G87" s="101" t="n"/>
-      <c r="H87" s="109" t="n"/>
-      <c r="I87" s="113" t="n"/>
+      <c r="B87" s="67" t="n"/>
+      <c r="C87" s="1" t="n"/>
+      <c r="D87" s="35" t="n"/>
+      <c r="E87" s="1" t="n"/>
+      <c r="F87" s="148" t="n"/>
+      <c r="G87" s="133" t="n"/>
+      <c r="H87" s="149" t="n"/>
+      <c r="I87" s="150" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1" s="41">
       <c r="A88" s="28" t="n"/>
-      <c r="B88" s="68" t="n"/>
-      <c r="C88" s="69" t="n"/>
-      <c r="D88" s="69" t="n"/>
-      <c r="E88" s="72" t="n"/>
-      <c r="F88" s="102" t="n"/>
-      <c r="G88" s="101" t="n"/>
-      <c r="H88" s="109" t="n"/>
-      <c r="I88" s="113" t="n"/>
+      <c r="B88" s="67" t="n"/>
+      <c r="C88" s="1" t="n"/>
+      <c r="D88" s="35" t="n"/>
+      <c r="E88" s="27" t="n"/>
+      <c r="F88" s="151" t="n"/>
+      <c r="G88" s="123" t="n"/>
+      <c r="H88" s="152" t="n"/>
+      <c r="I88" s="150" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1" s="41">
       <c r="A89" s="28" t="n"/>
-      <c r="B89" s="68" t="n"/>
-      <c r="C89" s="69" t="n"/>
-      <c r="D89" s="69" t="n"/>
-      <c r="E89" s="72" t="n"/>
-      <c r="F89" s="102" t="n"/>
-      <c r="G89" s="101" t="n"/>
-      <c r="H89" s="109" t="n"/>
-      <c r="I89" s="113" t="n"/>
+      <c r="B89" s="67" t="n"/>
+      <c r="C89" s="1" t="n"/>
+      <c r="D89" s="35" t="n"/>
+      <c r="E89" s="1" t="n"/>
+      <c r="F89" s="148" t="n"/>
+      <c r="G89" s="133" t="n"/>
+      <c r="H89" s="149" t="n"/>
+      <c r="I89" s="150" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1" s="41">
       <c r="A90" s="28" t="n"/>
-      <c r="B90" s="68" t="n"/>
-      <c r="C90" s="69" t="n"/>
-      <c r="D90" s="69" t="n"/>
-      <c r="E90" s="72" t="n"/>
-      <c r="F90" s="102" t="n"/>
-      <c r="G90" s="101" t="n"/>
-      <c r="H90" s="109" t="n"/>
-      <c r="I90" s="113" t="n"/>
+      <c r="B90" s="67" t="n"/>
+      <c r="C90" s="1" t="n"/>
+      <c r="D90" s="35" t="n"/>
+      <c r="E90" s="27" t="n"/>
+      <c r="F90" s="151" t="n"/>
+      <c r="G90" s="123" t="n"/>
+      <c r="H90" s="152" t="n"/>
+      <c r="I90" s="150" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1" s="41">
       <c r="A91" s="28" t="n"/>
-      <c r="B91" s="68" t="n"/>
-      <c r="C91" s="69" t="n"/>
-      <c r="D91" s="69" t="n"/>
-      <c r="E91" s="72" t="n"/>
-      <c r="F91" s="102" t="n"/>
-      <c r="G91" s="101" t="n"/>
-      <c r="H91" s="109" t="n"/>
-      <c r="I91" s="113" t="n"/>
+      <c r="B91" s="67" t="n"/>
+      <c r="C91" s="1" t="n"/>
+      <c r="D91" s="35" t="n"/>
+      <c r="E91" s="1" t="n"/>
+      <c r="F91" s="148" t="n"/>
+      <c r="G91" s="133" t="n"/>
+      <c r="H91" s="149" t="n"/>
+      <c r="I91" s="150" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1" s="41">
       <c r="A92" s="28" t="n"/>
-      <c r="B92" s="68" t="n"/>
-      <c r="C92" s="69" t="n"/>
-      <c r="D92" s="69" t="n"/>
-      <c r="E92" s="72" t="n"/>
-      <c r="F92" s="102" t="n"/>
-      <c r="G92" s="101" t="n"/>
-      <c r="H92" s="109" t="n"/>
-      <c r="I92" s="113" t="n"/>
+      <c r="B92" s="67" t="n"/>
+      <c r="C92" s="1" t="n"/>
+      <c r="D92" s="35" t="n"/>
+      <c r="E92" s="27" t="n"/>
+      <c r="F92" s="151" t="n"/>
+      <c r="G92" s="123" t="n"/>
+      <c r="H92" s="152" t="n"/>
+      <c r="I92" s="150" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1" s="41">
       <c r="A93" s="28" t="n"/>
-      <c r="B93" s="68" t="n"/>
-      <c r="C93" s="69" t="n"/>
-      <c r="D93" s="69" t="n"/>
-      <c r="E93" s="69" t="n"/>
-      <c r="F93" s="132" t="n"/>
+      <c r="B93" s="67" t="n"/>
+      <c r="C93" s="1" t="n"/>
+      <c r="D93" s="35" t="n"/>
+      <c r="E93" s="1" t="n"/>
+      <c r="F93" s="148" t="n"/>
       <c r="G93" s="133" t="n"/>
-      <c r="H93" s="110" t="n"/>
-      <c r="I93" s="113" t="n"/>
+      <c r="H93" s="149" t="n"/>
+      <c r="I93" s="150" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1" s="41">
       <c r="A94" s="28" t="n"/>
-      <c r="B94" s="68" t="n"/>
-      <c r="C94" s="69" t="n"/>
-      <c r="D94" s="69" t="n"/>
-      <c r="E94" s="70" t="n"/>
-      <c r="F94" s="136" t="n"/>
-      <c r="G94" s="137" t="n"/>
-      <c r="H94" s="109" t="n"/>
-      <c r="I94" s="113" t="n"/>
+      <c r="B94" s="67" t="n"/>
+      <c r="C94" s="1" t="n"/>
+      <c r="D94" s="35" t="n"/>
+      <c r="E94" s="27" t="n"/>
+      <c r="F94" s="151" t="n"/>
+      <c r="G94" s="123" t="n"/>
+      <c r="H94" s="152" t="n"/>
+      <c r="I94" s="150" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1" s="41">
       <c r="A95" s="28" t="n"/>
-      <c r="B95" s="68" t="n"/>
-      <c r="C95" s="69" t="n"/>
-      <c r="D95" s="69" t="n"/>
-      <c r="E95" s="69" t="n"/>
-      <c r="F95" s="139" t="n"/>
+      <c r="B95" s="67" t="n"/>
+      <c r="C95" s="1" t="n"/>
+      <c r="D95" s="35" t="n"/>
+      <c r="E95" s="1" t="n"/>
+      <c r="F95" s="153" t="n"/>
       <c r="G95" s="119" t="n"/>
-      <c r="H95" s="110" t="n"/>
-      <c r="I95" s="113" t="n"/>
+      <c r="H95" s="149" t="n"/>
+      <c r="I95" s="150" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="41">
       <c r="A96" s="28" t="n"/>
-      <c r="B96" s="68" t="n"/>
-      <c r="C96" s="69" t="n"/>
-      <c r="D96" s="73" t="n"/>
-      <c r="E96" s="70" t="n"/>
-      <c r="F96" s="130" t="n"/>
+      <c r="B96" s="67" t="n"/>
+      <c r="C96" s="1" t="n"/>
+      <c r="D96" s="35" t="n"/>
+      <c r="E96" s="27" t="n"/>
+      <c r="F96" s="151" t="n"/>
       <c r="G96" s="123" t="n"/>
-      <c r="H96" s="109" t="n"/>
-      <c r="I96" s="113" t="n"/>
+      <c r="H96" s="152" t="n"/>
+      <c r="I96" s="150" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1" s="41">
       <c r="A97" s="28" t="n"/>
-      <c r="B97" s="68" t="n"/>
-      <c r="C97" s="70" t="n"/>
-      <c r="D97" s="74" t="n"/>
-      <c r="E97" s="75" t="n"/>
-      <c r="F97" s="130" t="n"/>
-      <c r="G97" s="123" t="n"/>
-      <c r="H97" s="109" t="n"/>
-      <c r="I97" s="113" t="n"/>
+      <c r="B97" s="67" t="n"/>
+      <c r="C97" s="1" t="n"/>
+      <c r="D97" s="35" t="n"/>
+      <c r="E97" s="1" t="n"/>
+      <c r="F97" s="148" t="n"/>
+      <c r="G97" s="133" t="n"/>
+      <c r="H97" s="149" t="n"/>
+      <c r="I97" s="150" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1" s="41">
       <c r="A98" s="28" t="n"/>
-      <c r="B98" s="68" t="n"/>
-      <c r="C98" s="70" t="n"/>
-      <c r="D98" s="76" t="n"/>
-      <c r="E98" s="75" t="n"/>
-      <c r="F98" s="130" t="n"/>
+      <c r="B98" s="67" t="n"/>
+      <c r="C98" s="1" t="n"/>
+      <c r="D98" s="35" t="n"/>
+      <c r="E98" s="27" t="n"/>
+      <c r="F98" s="151" t="n"/>
       <c r="G98" s="123" t="n"/>
-      <c r="H98" s="109" t="n"/>
-      <c r="I98" s="113" t="n"/>
+      <c r="H98" s="152" t="n"/>
+      <c r="I98" s="150" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1" s="41">
       <c r="A99" s="28" t="n"/>
-      <c r="B99" s="68" t="n"/>
-      <c r="C99" s="70" t="n"/>
-      <c r="D99" s="77" t="n"/>
-      <c r="E99" s="75" t="n"/>
-      <c r="F99" s="130" t="n"/>
-      <c r="G99" s="123" t="n"/>
-      <c r="H99" s="109" t="n"/>
-      <c r="I99" s="113" t="n"/>
+      <c r="B99" s="67" t="n"/>
+      <c r="C99" s="1" t="n"/>
+      <c r="D99" s="35" t="n"/>
+      <c r="E99" s="1" t="n"/>
+      <c r="F99" s="148" t="n"/>
+      <c r="G99" s="133" t="n"/>
+      <c r="H99" s="149" t="n"/>
+      <c r="I99" s="150" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="41">
       <c r="A100" s="28" t="n"/>
-      <c r="B100" s="68" t="n"/>
-      <c r="C100" s="70" t="n"/>
-      <c r="D100" s="78" t="n"/>
-      <c r="E100" s="75" t="n"/>
-      <c r="F100" s="130" t="n"/>
+      <c r="B100" s="67" t="n"/>
+      <c r="C100" s="1" t="n"/>
+      <c r="D100" s="35" t="n"/>
+      <c r="E100" s="27" t="n"/>
+      <c r="F100" s="151" t="n"/>
       <c r="G100" s="123" t="n"/>
-      <c r="H100" s="109" t="n"/>
-      <c r="I100" s="113" t="n"/>
+      <c r="H100" s="152" t="n"/>
+      <c r="I100" s="150" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="41">
       <c r="A101" s="28" t="n"/>
-      <c r="B101" s="68" t="n"/>
-      <c r="C101" s="70" t="n"/>
-      <c r="D101" s="77" t="n"/>
-      <c r="E101" s="75" t="n"/>
-      <c r="F101" s="130" t="n"/>
-      <c r="G101" s="123" t="n"/>
-      <c r="H101" s="109" t="n"/>
-      <c r="I101" s="113" t="n"/>
+      <c r="B101" s="67" t="n"/>
+      <c r="C101" s="1" t="n"/>
+      <c r="D101" s="35" t="n"/>
+      <c r="E101" s="1" t="n"/>
+      <c r="F101" s="148" t="n"/>
+      <c r="G101" s="133" t="n"/>
+      <c r="H101" s="149" t="n"/>
+      <c r="I101" s="150" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1" s="41">
       <c r="A102" s="28" t="n"/>
-      <c r="B102" s="68" t="n"/>
-      <c r="C102" s="72" t="n"/>
-      <c r="D102" s="79" t="n"/>
-      <c r="E102" s="75" t="n"/>
-      <c r="F102" s="107" t="n"/>
-      <c r="G102" s="103" t="n"/>
-      <c r="H102" s="109" t="n"/>
-      <c r="I102" s="113" t="n"/>
+      <c r="B102" s="67" t="n"/>
+      <c r="C102" s="1" t="n"/>
+      <c r="D102" s="35" t="n"/>
+      <c r="E102" s="27" t="n"/>
+      <c r="F102" s="151" t="n"/>
+      <c r="G102" s="123" t="n"/>
+      <c r="H102" s="152" t="n"/>
+      <c r="I102" s="150" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1" s="41">
       <c r="A103" s="28" t="n"/>
-      <c r="B103" s="68" t="n"/>
-      <c r="C103" s="72" t="n"/>
-      <c r="D103" s="77" t="n"/>
-      <c r="E103" s="75" t="n"/>
-      <c r="F103" s="130" t="n"/>
-      <c r="G103" s="123" t="n"/>
-      <c r="H103" s="109" t="n"/>
-      <c r="I103" s="113" t="n"/>
+      <c r="B103" s="67" t="n"/>
+      <c r="C103" s="1" t="n"/>
+      <c r="D103" s="35" t="n"/>
+      <c r="E103" s="1" t="n"/>
+      <c r="F103" s="148" t="n"/>
+      <c r="G103" s="133" t="n"/>
+      <c r="H103" s="149" t="n"/>
+      <c r="I103" s="150" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1" s="41">
       <c r="A104" s="28" t="n"/>
-      <c r="B104" s="68" t="n"/>
-      <c r="C104" s="72" t="n"/>
-      <c r="D104" s="79" t="n"/>
-      <c r="E104" s="75" t="n"/>
-      <c r="F104" s="107" t="n"/>
-      <c r="G104" s="103" t="n"/>
-      <c r="H104" s="109" t="n"/>
-      <c r="I104" s="113" t="n"/>
+      <c r="B104" s="67" t="n"/>
+      <c r="C104" s="1" t="n"/>
+      <c r="D104" s="35" t="n"/>
+      <c r="E104" s="27" t="n"/>
+      <c r="F104" s="151" t="n"/>
+      <c r="G104" s="123" t="n"/>
+      <c r="H104" s="152" t="n"/>
+      <c r="I104" s="150" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1" s="41" thickBot="1">
       <c r="A105" s="28" t="n"/>
-      <c r="B105" s="42" t="inlineStr">
+      <c r="B105" s="67" t="inlineStr">
         <is>
           <t>TOTAIS</t>
         </is>
       </c>
-      <c r="C105" s="140" t="n"/>
-      <c r="D105" s="140" t="n"/>
-      <c r="E105" s="141" t="n"/>
-      <c r="F105" s="142">
+      <c r="C105" s="156" t="n"/>
+      <c r="D105" s="156" t="n"/>
+      <c r="E105" s="157" t="n"/>
+      <c r="F105" s="153">
         <f>SUM(F9:F104)</f>
         <v/>
       </c>
-      <c r="G105" s="44" t="n"/>
-      <c r="H105" s="31">
+      <c r="G105" s="119" t="n"/>
+      <c r="H105" s="149">
         <f>SUM(H9:H104)</f>
         <v/>
       </c>
-      <c r="I105" s="32">
+      <c r="I105" s="150">
         <f>SUM(I9:I104)</f>
         <v/>
       </c>
       <c r="J105" s="30" t="n"/>
     </row>
+    <row r="106">
+      <c r="B106" s="67" t="n"/>
+      <c r="C106" s="1" t="n"/>
+      <c r="D106" s="35" t="n"/>
+      <c r="E106" s="27" t="n"/>
+      <c r="F106" s="151" t="n"/>
+      <c r="G106" s="123" t="n"/>
+      <c r="H106" s="152" t="n"/>
+      <c r="I106" s="150" t="n"/>
+    </row>
     <row r="107">
-      <c r="B107" s="40" t="inlineStr">
+      <c r="B107" s="67" t="inlineStr">
         <is>
           <t>LEGENDA DE CORES — Atraso: ■ Vermelho ≥180 dias   ■ Laranja 60-179 dias   ■ Amarelo &lt;60 dias   |   Valor: ■ Azul = Original   ■ Vermelho = Juros   ■ Verde = Total</t>
         </is>
       </c>
+      <c r="C107" s="156" t="n"/>
+      <c r="D107" s="156" t="n"/>
+      <c r="E107" s="156" t="n"/>
+      <c r="F107" s="156" t="n"/>
+      <c r="G107" s="156" t="n"/>
+      <c r="H107" s="156" t="n"/>
+      <c r="I107" s="157" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="67" t="n"/>
+      <c r="C108" s="1" t="n"/>
+      <c r="D108" s="35" t="n"/>
+      <c r="E108" s="27" t="n"/>
+      <c r="F108" s="151" t="n"/>
+      <c r="G108" s="123" t="n"/>
+      <c r="H108" s="152" t="n"/>
+      <c r="I108" s="150" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="67" t="n"/>
+      <c r="C109" s="1" t="n"/>
+      <c r="D109" s="35" t="n"/>
+      <c r="E109" s="1" t="n"/>
+      <c r="F109" s="153" t="n"/>
+      <c r="G109" s="119" t="n"/>
+      <c r="H109" s="149" t="n"/>
+      <c r="I109" s="150" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="67" t="n"/>
+      <c r="C110" s="1" t="n"/>
+      <c r="D110" s="35" t="n"/>
+      <c r="E110" s="27" t="n"/>
+      <c r="F110" s="151" t="n"/>
+      <c r="G110" s="123" t="n"/>
+      <c r="H110" s="152" t="n"/>
+      <c r="I110" s="150" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="67" t="n"/>
+      <c r="C111" s="1" t="n"/>
+      <c r="D111" s="35" t="n"/>
+      <c r="E111" s="1" t="n"/>
+      <c r="F111" s="153" t="n"/>
+      <c r="G111" s="119" t="n"/>
+      <c r="H111" s="149" t="n"/>
+      <c r="I111" s="150" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="67" t="n"/>
+      <c r="C112" s="1" t="n"/>
+      <c r="D112" s="35" t="n"/>
+      <c r="E112" s="27" t="n"/>
+      <c r="F112" s="151" t="n"/>
+      <c r="G112" s="123" t="n"/>
+      <c r="H112" s="152" t="n"/>
+      <c r="I112" s="150" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="67" t="n"/>
+      <c r="C113" s="1" t="n"/>
+      <c r="D113" s="35" t="n"/>
+      <c r="E113" s="1" t="n"/>
+      <c r="F113" s="153" t="n"/>
+      <c r="G113" s="119" t="n"/>
+      <c r="H113" s="149" t="n"/>
+      <c r="I113" s="150" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="67" t="n"/>
+      <c r="C114" s="1" t="n"/>
+      <c r="D114" s="35" t="n"/>
+      <c r="E114" s="27" t="n"/>
+      <c r="F114" s="151" t="n"/>
+      <c r="G114" s="123" t="n"/>
+      <c r="H114" s="152" t="n"/>
+      <c r="I114" s="150" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="67" t="n"/>
+      <c r="C115" s="1" t="n"/>
+      <c r="D115" s="35" t="n"/>
+      <c r="E115" s="1" t="n"/>
+      <c r="F115" s="153" t="n"/>
+      <c r="G115" s="119" t="n"/>
+      <c r="H115" s="149" t="n"/>
+      <c r="I115" s="150" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="67" t="n"/>
+      <c r="C116" s="1" t="n"/>
+      <c r="D116" s="35" t="n"/>
+      <c r="E116" s="27" t="n"/>
+      <c r="F116" s="151" t="n"/>
+      <c r="G116" s="123" t="n"/>
+      <c r="H116" s="152" t="n"/>
+      <c r="I116" s="150" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="67" t="n"/>
+      <c r="C117" s="1" t="n"/>
+      <c r="D117" s="35" t="n"/>
+      <c r="E117" s="1" t="n"/>
+      <c r="F117" s="153" t="n"/>
+      <c r="G117" s="119" t="n"/>
+      <c r="H117" s="149" t="n"/>
+      <c r="I117" s="150" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="67" t="n"/>
+      <c r="C118" s="1" t="n"/>
+      <c r="D118" s="35" t="n"/>
+      <c r="E118" s="27" t="n"/>
+      <c r="F118" s="151" t="n"/>
+      <c r="G118" s="123" t="n"/>
+      <c r="H118" s="152" t="n"/>
+      <c r="I118" s="150" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="67" t="n"/>
+      <c r="C119" s="1" t="n"/>
+      <c r="D119" s="35" t="n"/>
+      <c r="E119" s="1" t="n"/>
+      <c r="F119" s="153" t="n"/>
+      <c r="G119" s="119" t="n"/>
+      <c r="H119" s="149" t="n"/>
+      <c r="I119" s="150" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="67" t="n"/>
+      <c r="C120" s="1" t="n"/>
+      <c r="D120" s="35" t="n"/>
+      <c r="E120" s="27" t="n"/>
+      <c r="F120" s="151" t="n"/>
+      <c r="G120" s="123" t="n"/>
+      <c r="H120" s="152" t="n"/>
+      <c r="I120" s="150" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="67" t="n"/>
+      <c r="C121" s="1" t="n"/>
+      <c r="D121" s="35" t="n"/>
+      <c r="E121" s="1" t="n"/>
+      <c r="F121" s="153" t="n"/>
+      <c r="G121" s="119" t="n"/>
+      <c r="H121" s="149" t="n"/>
+      <c r="I121" s="150" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="67" t="n"/>
+      <c r="C122" s="1" t="n"/>
+      <c r="D122" s="35" t="n"/>
+      <c r="E122" s="27" t="n"/>
+      <c r="F122" s="151" t="n"/>
+      <c r="G122" s="123" t="n"/>
+      <c r="H122" s="152" t="n"/>
+      <c r="I122" s="150" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="67" t="n"/>
+      <c r="C123" s="1" t="n"/>
+      <c r="D123" s="35" t="n"/>
+      <c r="E123" s="1" t="n"/>
+      <c r="F123" s="153" t="n"/>
+      <c r="G123" s="119" t="n"/>
+      <c r="H123" s="149" t="n"/>
+      <c r="I123" s="150" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="67" t="n"/>
+      <c r="C124" s="1" t="n"/>
+      <c r="D124" s="35" t="n"/>
+      <c r="E124" s="27" t="n"/>
+      <c r="F124" s="151" t="n"/>
+      <c r="G124" s="123" t="n"/>
+      <c r="H124" s="152" t="n"/>
+      <c r="I124" s="150" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="67" t="n"/>
+      <c r="C125" s="1" t="n"/>
+      <c r="D125" s="35" t="n"/>
+      <c r="E125" s="1" t="n"/>
+      <c r="F125" s="153" t="n"/>
+      <c r="G125" s="119" t="n"/>
+      <c r="H125" s="149" t="n"/>
+      <c r="I125" s="150" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="67" t="n"/>
+      <c r="C126" s="1" t="n"/>
+      <c r="D126" s="35" t="n"/>
+      <c r="E126" s="27" t="n"/>
+      <c r="F126" s="151" t="n"/>
+      <c r="G126" s="123" t="n"/>
+      <c r="H126" s="152" t="n"/>
+      <c r="I126" s="150" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="67" t="n"/>
+      <c r="C127" s="1" t="n"/>
+      <c r="D127" s="35" t="n"/>
+      <c r="E127" s="1" t="n"/>
+      <c r="F127" s="153" t="n"/>
+      <c r="G127" s="119" t="n"/>
+      <c r="H127" s="149" t="n"/>
+      <c r="I127" s="150" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="67" t="n"/>
+      <c r="C128" s="1" t="n"/>
+      <c r="D128" s="35" t="n"/>
+      <c r="E128" s="27" t="n"/>
+      <c r="F128" s="151" t="n"/>
+      <c r="G128" s="123" t="n"/>
+      <c r="H128" s="152" t="n"/>
+      <c r="I128" s="150" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="67" t="n"/>
+      <c r="C129" s="1" t="n"/>
+      <c r="D129" s="35" t="n"/>
+      <c r="E129" s="1" t="n"/>
+      <c r="F129" s="153" t="n"/>
+      <c r="G129" s="119" t="n"/>
+      <c r="H129" s="149" t="n"/>
+      <c r="I129" s="150" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="67" t="n"/>
+      <c r="C130" s="1" t="n"/>
+      <c r="D130" s="35" t="n"/>
+      <c r="E130" s="27" t="n"/>
+      <c r="F130" s="151" t="n"/>
+      <c r="G130" s="123" t="n"/>
+      <c r="H130" s="152" t="n"/>
+      <c r="I130" s="150" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="67" t="n"/>
+      <c r="C131" s="1" t="n"/>
+      <c r="D131" s="35" t="n"/>
+      <c r="E131" s="1" t="n"/>
+      <c r="F131" s="153" t="n"/>
+      <c r="G131" s="119" t="n"/>
+      <c r="H131" s="149" t="n"/>
+      <c r="I131" s="150" t="n"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="67" t="n"/>
+      <c r="C132" s="1" t="n"/>
+      <c r="D132" s="35" t="n"/>
+      <c r="E132" s="27" t="n"/>
+      <c r="F132" s="151" t="n"/>
+      <c r="G132" s="123" t="n"/>
+      <c r="H132" s="152" t="n"/>
+      <c r="I132" s="150" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="67" t="n"/>
+      <c r="C133" s="1" t="n"/>
+      <c r="D133" s="35" t="n"/>
+      <c r="E133" s="1" t="n"/>
+      <c r="F133" s="153" t="n"/>
+      <c r="G133" s="119" t="n"/>
+      <c r="H133" s="149" t="n"/>
+      <c r="I133" s="150" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="67" t="n"/>
+      <c r="C134" s="1" t="n"/>
+      <c r="D134" s="35" t="n"/>
+      <c r="E134" s="27" t="n"/>
+      <c r="F134" s="151" t="n"/>
+      <c r="G134" s="123" t="n"/>
+      <c r="H134" s="152" t="n"/>
+      <c r="I134" s="150" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="67" t="n"/>
+      <c r="C135" s="1" t="n"/>
+      <c r="D135" s="35" t="n"/>
+      <c r="E135" s="1" t="n"/>
+      <c r="F135" s="153" t="n"/>
+      <c r="G135" s="119" t="n"/>
+      <c r="H135" s="149" t="n"/>
+      <c r="I135" s="150" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="67" t="n"/>
+      <c r="C136" s="1" t="n"/>
+      <c r="D136" s="35" t="n"/>
+      <c r="E136" s="27" t="n"/>
+      <c r="F136" s="151" t="n"/>
+      <c r="G136" s="123" t="n"/>
+      <c r="H136" s="152" t="n"/>
+      <c r="I136" s="150" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="67" t="n"/>
+      <c r="C137" s="1" t="n"/>
+      <c r="D137" s="35" t="n"/>
+      <c r="E137" s="1" t="n"/>
+      <c r="F137" s="153" t="n"/>
+      <c r="G137" s="119" t="n"/>
+      <c r="H137" s="149" t="n"/>
+      <c r="I137" s="150" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="67" t="n"/>
+      <c r="C138" s="1" t="n"/>
+      <c r="D138" s="35" t="n"/>
+      <c r="E138" s="27" t="n"/>
+      <c r="F138" s="151" t="n"/>
+      <c r="G138" s="123" t="n"/>
+      <c r="H138" s="152" t="n"/>
+      <c r="I138" s="150" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="67" t="n"/>
+      <c r="C139" s="1" t="n"/>
+      <c r="D139" s="35" t="n"/>
+      <c r="E139" s="1" t="n"/>
+      <c r="F139" s="153" t="n"/>
+      <c r="G139" s="119" t="n"/>
+      <c r="H139" s="149" t="n"/>
+      <c r="I139" s="150" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="67" t="n"/>
+      <c r="C140" s="1" t="n"/>
+      <c r="D140" s="35" t="n"/>
+      <c r="E140" s="27" t="n"/>
+      <c r="F140" s="151" t="n"/>
+      <c r="G140" s="123" t="n"/>
+      <c r="H140" s="152" t="n"/>
+      <c r="I140" s="150" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="67" t="n"/>
+      <c r="C141" s="1" t="n"/>
+      <c r="D141" s="35" t="n"/>
+      <c r="E141" s="1" t="n"/>
+      <c r="F141" s="153" t="n"/>
+      <c r="G141" s="119" t="n"/>
+      <c r="H141" s="149" t="n"/>
+      <c r="I141" s="150" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="67" t="n"/>
+      <c r="C142" s="1" t="n"/>
+      <c r="D142" s="35" t="n"/>
+      <c r="E142" s="27" t="n"/>
+      <c r="F142" s="151" t="n"/>
+      <c r="G142" s="123" t="n"/>
+      <c r="H142" s="152" t="n"/>
+      <c r="I142" s="150" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="67" t="n"/>
+      <c r="C143" s="1" t="n"/>
+      <c r="D143" s="35" t="n"/>
+      <c r="E143" s="1" t="n"/>
+      <c r="F143" s="153" t="n"/>
+      <c r="G143" s="119" t="n"/>
+      <c r="H143" s="149" t="n"/>
+      <c r="I143" s="150" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="67" t="n"/>
+      <c r="C144" s="1" t="n"/>
+      <c r="D144" s="35" t="n"/>
+      <c r="E144" s="27" t="n"/>
+      <c r="F144" s="151" t="n"/>
+      <c r="G144" s="123" t="n"/>
+      <c r="H144" s="152" t="n"/>
+      <c r="I144" s="150" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="67" t="n"/>
+      <c r="C145" s="1" t="n"/>
+      <c r="D145" s="35" t="n"/>
+      <c r="E145" s="1" t="n"/>
+      <c r="F145" s="153" t="n"/>
+      <c r="G145" s="119" t="n"/>
+      <c r="H145" s="149" t="n"/>
+      <c r="I145" s="150" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="67" t="n"/>
+      <c r="C146" s="1" t="n"/>
+      <c r="D146" s="35" t="n"/>
+      <c r="E146" s="27" t="n"/>
+      <c r="F146" s="151" t="n"/>
+      <c r="G146" s="123" t="n"/>
+      <c r="H146" s="152" t="n"/>
+      <c r="I146" s="150" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="67" t="n"/>
+      <c r="C147" s="1" t="n"/>
+      <c r="D147" s="35" t="n"/>
+      <c r="E147" s="1" t="n"/>
+      <c r="F147" s="153" t="n"/>
+      <c r="G147" s="119" t="n"/>
+      <c r="H147" s="149" t="n"/>
+      <c r="I147" s="150" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="67" t="n"/>
+      <c r="C148" s="1" t="n"/>
+      <c r="D148" s="35" t="n"/>
+      <c r="E148" s="27" t="n"/>
+      <c r="F148" s="151" t="n"/>
+      <c r="G148" s="123" t="n"/>
+      <c r="H148" s="152" t="n"/>
+      <c r="I148" s="150" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="67" t="n"/>
+      <c r="C149" s="1" t="n"/>
+      <c r="D149" s="35" t="n"/>
+      <c r="E149" s="1" t="n"/>
+      <c r="F149" s="153" t="n"/>
+      <c r="G149" s="119" t="n"/>
+      <c r="H149" s="149" t="n"/>
+      <c r="I149" s="150" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="67" t="n"/>
+      <c r="C150" s="1" t="n"/>
+      <c r="D150" s="35" t="n"/>
+      <c r="E150" s="27" t="n"/>
+      <c r="F150" s="151" t="n"/>
+      <c r="G150" s="123" t="n"/>
+      <c r="H150" s="152" t="n"/>
+      <c r="I150" s="150" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="67" t="n"/>
+      <c r="C151" s="1" t="n"/>
+      <c r="D151" s="35" t="n"/>
+      <c r="E151" s="1" t="n"/>
+      <c r="F151" s="153" t="n"/>
+      <c r="G151" s="119" t="n"/>
+      <c r="H151" s="149" t="n"/>
+      <c r="I151" s="150" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="67" t="n"/>
+      <c r="C152" s="1" t="n"/>
+      <c r="D152" s="35" t="n"/>
+      <c r="E152" s="27" t="n"/>
+      <c r="F152" s="151" t="n"/>
+      <c r="G152" s="123" t="n"/>
+      <c r="H152" s="152" t="n"/>
+      <c r="I152" s="150" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="67" t="n"/>
+      <c r="C153" s="1" t="n"/>
+      <c r="D153" s="35" t="n"/>
+      <c r="E153" s="1" t="n"/>
+      <c r="F153" s="153" t="n"/>
+      <c r="G153" s="119" t="n"/>
+      <c r="H153" s="149" t="n"/>
+      <c r="I153" s="150" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="67" t="n"/>
+      <c r="C154" s="1" t="n"/>
+      <c r="D154" s="35" t="n"/>
+      <c r="E154" s="27" t="n"/>
+      <c r="F154" s="151" t="n"/>
+      <c r="G154" s="123" t="n"/>
+      <c r="H154" s="152" t="n"/>
+      <c r="I154" s="150" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="67" t="n"/>
+      <c r="C155" s="1" t="n"/>
+      <c r="D155" s="35" t="n"/>
+      <c r="E155" s="1" t="n"/>
+      <c r="F155" s="153" t="n"/>
+      <c r="G155" s="119" t="n"/>
+      <c r="H155" s="149" t="n"/>
+      <c r="I155" s="150" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="67" t="n"/>
+      <c r="C156" s="1" t="n"/>
+      <c r="D156" s="35" t="n"/>
+      <c r="E156" s="27" t="n"/>
+      <c r="F156" s="151" t="n"/>
+      <c r="G156" s="123" t="n"/>
+      <c r="H156" s="152" t="n"/>
+      <c r="I156" s="150" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="67" t="n"/>
+      <c r="C157" s="1" t="n"/>
+      <c r="D157" s="35" t="n"/>
+      <c r="E157" s="1" t="n"/>
+      <c r="F157" s="153" t="n"/>
+      <c r="G157" s="119" t="n"/>
+      <c r="H157" s="149" t="n"/>
+      <c r="I157" s="150" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="67" t="n"/>
+      <c r="C158" s="1" t="n"/>
+      <c r="D158" s="35" t="n"/>
+      <c r="E158" s="27" t="n"/>
+      <c r="F158" s="151" t="n"/>
+      <c r="G158" s="123" t="n"/>
+      <c r="H158" s="152" t="n"/>
+      <c r="I158" s="150" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="67" t="n"/>
+      <c r="C159" s="1" t="n"/>
+      <c r="D159" s="35" t="n"/>
+      <c r="E159" s="1" t="n"/>
+      <c r="F159" s="153" t="n"/>
+      <c r="G159" s="119" t="n"/>
+      <c r="H159" s="149" t="n"/>
+      <c r="I159" s="150" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="67" t="n"/>
+      <c r="C160" s="1" t="n"/>
+      <c r="D160" s="35" t="n"/>
+      <c r="E160" s="27" t="n"/>
+      <c r="F160" s="151" t="n"/>
+      <c r="G160" s="123" t="n"/>
+      <c r="H160" s="152" t="n"/>
+      <c r="I160" s="150" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="67" t="n"/>
+      <c r="C161" s="1" t="n"/>
+      <c r="D161" s="35" t="n"/>
+      <c r="E161" s="1" t="n"/>
+      <c r="F161" s="153" t="n"/>
+      <c r="G161" s="119" t="n"/>
+      <c r="H161" s="149" t="n"/>
+      <c r="I161" s="150" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="67" t="n"/>
+      <c r="C162" s="1" t="n"/>
+      <c r="D162" s="35" t="n"/>
+      <c r="E162" s="27" t="n"/>
+      <c r="F162" s="151" t="n"/>
+      <c r="G162" s="123" t="n"/>
+      <c r="H162" s="152" t="n"/>
+      <c r="I162" s="150" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="67" t="n"/>
+      <c r="C163" s="1" t="n"/>
+      <c r="D163" s="35" t="n"/>
+      <c r="E163" s="1" t="n"/>
+      <c r="F163" s="153" t="n"/>
+      <c r="G163" s="119" t="n"/>
+      <c r="H163" s="149" t="n"/>
+      <c r="I163" s="150" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="67" t="n"/>
+      <c r="C164" s="1" t="n"/>
+      <c r="D164" s="35" t="n"/>
+      <c r="E164" s="27" t="n"/>
+      <c r="F164" s="151" t="n"/>
+      <c r="G164" s="123" t="n"/>
+      <c r="H164" s="152" t="n"/>
+      <c r="I164" s="150" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="67" t="n"/>
+      <c r="C165" s="1" t="n"/>
+      <c r="D165" s="35" t="n"/>
+      <c r="E165" s="1" t="n"/>
+      <c r="F165" s="153" t="n"/>
+      <c r="G165" s="119" t="n"/>
+      <c r="H165" s="149" t="n"/>
+      <c r="I165" s="150" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="67" t="n"/>
+      <c r="C166" s="1" t="n"/>
+      <c r="D166" s="35" t="n"/>
+      <c r="E166" s="27" t="n"/>
+      <c r="F166" s="151" t="n"/>
+      <c r="G166" s="123" t="n"/>
+      <c r="H166" s="152" t="n"/>
+      <c r="I166" s="150" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="67" t="n"/>
+      <c r="C167" s="1" t="n"/>
+      <c r="D167" s="35" t="n"/>
+      <c r="E167" s="1" t="n"/>
+      <c r="F167" s="153" t="n"/>
+      <c r="G167" s="119" t="n"/>
+      <c r="H167" s="149" t="n"/>
+      <c r="I167" s="150" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="67" t="n"/>
+      <c r="C168" s="1" t="n"/>
+      <c r="D168" s="35" t="n"/>
+      <c r="E168" s="27" t="n"/>
+      <c r="F168" s="151" t="n"/>
+      <c r="G168" s="123" t="n"/>
+      <c r="H168" s="152" t="n"/>
+      <c r="I168" s="150" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="67" t="n"/>
+      <c r="C169" s="1" t="n"/>
+      <c r="D169" s="35" t="n"/>
+      <c r="E169" s="1" t="n"/>
+      <c r="F169" s="153" t="n"/>
+      <c r="G169" s="119" t="n"/>
+      <c r="H169" s="149" t="n"/>
+      <c r="I169" s="150" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="67" t="n"/>
+      <c r="C170" s="1" t="n"/>
+      <c r="D170" s="35" t="n"/>
+      <c r="E170" s="27" t="n"/>
+      <c r="F170" s="151" t="n"/>
+      <c r="G170" s="123" t="n"/>
+      <c r="H170" s="152" t="n"/>
+      <c r="I170" s="150" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="67" t="n"/>
+      <c r="C171" s="1" t="n"/>
+      <c r="D171" s="35" t="n"/>
+      <c r="E171" s="1" t="n"/>
+      <c r="F171" s="153" t="n"/>
+      <c r="G171" s="119" t="n"/>
+      <c r="H171" s="149" t="n"/>
+      <c r="I171" s="150" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="67" t="n"/>
+      <c r="C172" s="1" t="n"/>
+      <c r="D172" s="35" t="n"/>
+      <c r="E172" s="27" t="n"/>
+      <c r="F172" s="151" t="n"/>
+      <c r="G172" s="123" t="n"/>
+      <c r="H172" s="152" t="n"/>
+      <c r="I172" s="150" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="67" t="n"/>
+      <c r="C173" s="1" t="n"/>
+      <c r="D173" s="35" t="n"/>
+      <c r="E173" s="1" t="n"/>
+      <c r="F173" s="153" t="n"/>
+      <c r="G173" s="119" t="n"/>
+      <c r="H173" s="149" t="n"/>
+      <c r="I173" s="150" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="67" t="n"/>
+      <c r="C174" s="1" t="n"/>
+      <c r="D174" s="35" t="n"/>
+      <c r="E174" s="27" t="n"/>
+      <c r="F174" s="151" t="n"/>
+      <c r="G174" s="123" t="n"/>
+      <c r="H174" s="152" t="n"/>
+      <c r="I174" s="150" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="67" t="n"/>
+      <c r="C175" s="1" t="n"/>
+      <c r="D175" s="35" t="n"/>
+      <c r="E175" s="1" t="n"/>
+      <c r="F175" s="153" t="n"/>
+      <c r="G175" s="119" t="n"/>
+      <c r="H175" s="149" t="n"/>
+      <c r="I175" s="150" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="67" t="n"/>
+      <c r="C176" s="1" t="n"/>
+      <c r="D176" s="35" t="n"/>
+      <c r="E176" s="27" t="n"/>
+      <c r="F176" s="151" t="n"/>
+      <c r="G176" s="123" t="n"/>
+      <c r="H176" s="152" t="n"/>
+      <c r="I176" s="150" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="67" t="n"/>
+      <c r="C177" s="1" t="n"/>
+      <c r="D177" s="35" t="n"/>
+      <c r="E177" s="1" t="n"/>
+      <c r="F177" s="153" t="n"/>
+      <c r="G177" s="119" t="n"/>
+      <c r="H177" s="149" t="n"/>
+      <c r="I177" s="150" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="67" t="n"/>
+      <c r="C178" s="1" t="n"/>
+      <c r="D178" s="35" t="n"/>
+      <c r="E178" s="27" t="n"/>
+      <c r="F178" s="151" t="n"/>
+      <c r="G178" s="123" t="n"/>
+      <c r="H178" s="152" t="n"/>
+      <c r="I178" s="150" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="67" t="n"/>
+      <c r="C179" s="1" t="n"/>
+      <c r="D179" s="35" t="n"/>
+      <c r="E179" s="1" t="n"/>
+      <c r="F179" s="153" t="n"/>
+      <c r="G179" s="119" t="n"/>
+      <c r="H179" s="149" t="n"/>
+      <c r="I179" s="150" t="n"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="67" t="n"/>
+      <c r="C180" s="1" t="n"/>
+      <c r="D180" s="35" t="n"/>
+      <c r="E180" s="27" t="n"/>
+      <c r="F180" s="151" t="n"/>
+      <c r="G180" s="123" t="n"/>
+      <c r="H180" s="152" t="n"/>
+      <c r="I180" s="150" t="n"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="67" t="n"/>
+      <c r="C181" s="1" t="n"/>
+      <c r="D181" s="35" t="n"/>
+      <c r="E181" s="1" t="n"/>
+      <c r="F181" s="153" t="n"/>
+      <c r="G181" s="119" t="n"/>
+      <c r="H181" s="149" t="n"/>
+      <c r="I181" s="150" t="n"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="67" t="n"/>
+      <c r="C182" s="1" t="n"/>
+      <c r="D182" s="35" t="n"/>
+      <c r="E182" s="27" t="n"/>
+      <c r="F182" s="151" t="n"/>
+      <c r="G182" s="123" t="n"/>
+      <c r="H182" s="152" t="n"/>
+      <c r="I182" s="150" t="n"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="67" t="n"/>
+      <c r="C183" s="1" t="n"/>
+      <c r="D183" s="35" t="n"/>
+      <c r="E183" s="1" t="n"/>
+      <c r="F183" s="153" t="n"/>
+      <c r="G183" s="119" t="n"/>
+      <c r="H183" s="149" t="n"/>
+      <c r="I183" s="150" t="n"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="67" t="n"/>
+      <c r="C184" s="1" t="n"/>
+      <c r="D184" s="35" t="n"/>
+      <c r="E184" s="27" t="n"/>
+      <c r="F184" s="151" t="n"/>
+      <c r="G184" s="123" t="n"/>
+      <c r="H184" s="152" t="n"/>
+      <c r="I184" s="150" t="n"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="67" t="n"/>
+      <c r="C185" s="1" t="n"/>
+      <c r="D185" s="35" t="n"/>
+      <c r="E185" s="1" t="n"/>
+      <c r="F185" s="153" t="n"/>
+      <c r="G185" s="119" t="n"/>
+      <c r="H185" s="149" t="n"/>
+      <c r="I185" s="150" t="n"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="67" t="n"/>
+      <c r="C186" s="1" t="n"/>
+      <c r="D186" s="35" t="n"/>
+      <c r="E186" s="27" t="n"/>
+      <c r="F186" s="151" t="n"/>
+      <c r="G186" s="123" t="n"/>
+      <c r="H186" s="152" t="n"/>
+      <c r="I186" s="150" t="n"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="67" t="n"/>
+      <c r="C187" s="1" t="n"/>
+      <c r="D187" s="35" t="n"/>
+      <c r="E187" s="1" t="n"/>
+      <c r="F187" s="153" t="n"/>
+      <c r="G187" s="119" t="n"/>
+      <c r="H187" s="149" t="n"/>
+      <c r="I187" s="150" t="n"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="67" t="n"/>
+      <c r="C188" s="1" t="n"/>
+      <c r="D188" s="35" t="n"/>
+      <c r="E188" s="27" t="n"/>
+      <c r="F188" s="151" t="n"/>
+      <c r="G188" s="123" t="n"/>
+      <c r="H188" s="152" t="n"/>
+      <c r="I188" s="150" t="n"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="67" t="n"/>
+      <c r="C189" s="1" t="n"/>
+      <c r="D189" s="35" t="n"/>
+      <c r="E189" s="1" t="n"/>
+      <c r="F189" s="153" t="n"/>
+      <c r="G189" s="119" t="n"/>
+      <c r="H189" s="149" t="n"/>
+      <c r="I189" s="150" t="n"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="67" t="n"/>
+      <c r="C190" s="1" t="n"/>
+      <c r="D190" s="35" t="n"/>
+      <c r="E190" s="27" t="n"/>
+      <c r="F190" s="151" t="n"/>
+      <c r="G190" s="123" t="n"/>
+      <c r="H190" s="152" t="n"/>
+      <c r="I190" s="150" t="n"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="67" t="n"/>
+      <c r="C191" s="1" t="n"/>
+      <c r="D191" s="35" t="n"/>
+      <c r="E191" s="1" t="n"/>
+      <c r="F191" s="153" t="n"/>
+      <c r="G191" s="119" t="n"/>
+      <c r="H191" s="149" t="n"/>
+      <c r="I191" s="150" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="67" t="n"/>
+      <c r="C192" s="1" t="n"/>
+      <c r="D192" s="35" t="n"/>
+      <c r="E192" s="27" t="n"/>
+      <c r="F192" s="151" t="n"/>
+      <c r="G192" s="123" t="n"/>
+      <c r="H192" s="152" t="n"/>
+      <c r="I192" s="150" t="n"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="67" t="n"/>
+      <c r="C193" s="1" t="n"/>
+      <c r="D193" s="35" t="n"/>
+      <c r="E193" s="1" t="n"/>
+      <c r="F193" s="153" t="n"/>
+      <c r="G193" s="119" t="n"/>
+      <c r="H193" s="149" t="n"/>
+      <c r="I193" s="150" t="n"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="67" t="n"/>
+      <c r="C194" s="1" t="n"/>
+      <c r="D194" s="35" t="n"/>
+      <c r="E194" s="27" t="n"/>
+      <c r="F194" s="151" t="n"/>
+      <c r="G194" s="123" t="n"/>
+      <c r="H194" s="152" t="n"/>
+      <c r="I194" s="150" t="n"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="67" t="n"/>
+      <c r="C195" s="1" t="n"/>
+      <c r="D195" s="35" t="n"/>
+      <c r="E195" s="1" t="n"/>
+      <c r="F195" s="153" t="n"/>
+      <c r="G195" s="119" t="n"/>
+      <c r="H195" s="149" t="n"/>
+      <c r="I195" s="150" t="n"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="67" t="n"/>
+      <c r="C196" s="1" t="n"/>
+      <c r="D196" s="35" t="n"/>
+      <c r="E196" s="27" t="n"/>
+      <c r="F196" s="151" t="n"/>
+      <c r="G196" s="123" t="n"/>
+      <c r="H196" s="152" t="n"/>
+      <c r="I196" s="150" t="n"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="67" t="n"/>
+      <c r="C197" s="1" t="n"/>
+      <c r="D197" s="35" t="n"/>
+      <c r="E197" s="1" t="n"/>
+      <c r="F197" s="153" t="n"/>
+      <c r="G197" s="119" t="n"/>
+      <c r="H197" s="149" t="n"/>
+      <c r="I197" s="150" t="n"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="67" t="n"/>
+      <c r="C198" s="1" t="n"/>
+      <c r="D198" s="35" t="n"/>
+      <c r="E198" s="27" t="n"/>
+      <c r="F198" s="151" t="n"/>
+      <c r="G198" s="123" t="n"/>
+      <c r="H198" s="152" t="n"/>
+      <c r="I198" s="150" t="n"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="67" t="n"/>
+      <c r="C199" s="1" t="n"/>
+      <c r="D199" s="35" t="n"/>
+      <c r="E199" s="1" t="n"/>
+      <c r="F199" s="153" t="n"/>
+      <c r="G199" s="119" t="n"/>
+      <c r="H199" s="149" t="n"/>
+      <c r="I199" s="150" t="n"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="67" t="n"/>
+      <c r="C200" s="1" t="n"/>
+      <c r="D200" s="35" t="n"/>
+      <c r="E200" s="27" t="n"/>
+      <c r="F200" s="151" t="n"/>
+      <c r="G200" s="123" t="n"/>
+      <c r="H200" s="152" t="n"/>
+      <c r="I200" s="150" t="n"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="67" t="n"/>
+      <c r="C201" s="1" t="n"/>
+      <c r="D201" s="35" t="n"/>
+      <c r="E201" s="1" t="n"/>
+      <c r="F201" s="148" t="n"/>
+      <c r="G201" s="133" t="n"/>
+      <c r="H201" s="149" t="n"/>
+      <c r="I201" s="150" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="F11:G11"/>
+  <mergeCells count="179">
+    <mergeCell ref="F116:G116"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F172:G172"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F174:G174"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="F158:G158"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="F170:G170"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="F171:G171"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F19:G19"/>
     <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F19:G19"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="F146:G146"/>
     <mergeCell ref="F99:G99"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F7:G7"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F83:G83"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F138:G138"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B107:I107"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="F85:G85"/>
     <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F198:G198"/>
     <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F35:G35"/>
     <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F188:G188"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="F109:G109"/>
     <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="F190:G190"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F161:G161"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F192:G192"/>
+    <mergeCell ref="F201:G201"/>
+    <mergeCell ref="F164:G164"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F194:G194"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F163:G163"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="F181:G181"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="F156:G156"/>
+    <mergeCell ref="F165:G165"/>
+    <mergeCell ref="F180:G180"/>
+    <mergeCell ref="F141:G141"/>
     <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F115:G115"/>
     <mergeCell ref="F93:G93"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="F166:G166"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F182:G182"/>
+    <mergeCell ref="F191:G191"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="F183:G183"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="B107:I107"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F184:G184"/>
+    <mergeCell ref="F131:G131"/>
     <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F140:G140"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F39:G39"/>
     <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="F195:G195"/>
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="F179:G179"/>
+    <mergeCell ref="F157:G157"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="F53:G53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2986,7 +4100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I126"/>
+  <dimension ref="A2:I201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="41" min="1" max="1"/>
@@ -3751,476 +4865,1160 @@
       <c r="H74" s="6" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1" s="41">
-      <c r="B75" s="11" t="n"/>
-      <c r="C75" s="33" t="n"/>
-      <c r="D75" s="33" t="n"/>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="6" t="n"/>
+      <c r="B75" s="34" t="n"/>
+      <c r="C75" s="1" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="35" t="n"/>
+      <c r="F75" s="154" t="n"/>
+      <c r="G75" s="149" t="n"/>
+      <c r="H75" s="155" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1" s="41">
-      <c r="B76" s="11" t="n"/>
-      <c r="C76" s="33" t="n"/>
-      <c r="D76" s="33" t="n"/>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="6" t="n"/>
+      <c r="B76" s="34" t="n"/>
+      <c r="C76" s="1" t="n"/>
+      <c r="D76" s="1" t="n"/>
+      <c r="E76" s="35" t="n"/>
+      <c r="F76" s="154" t="n"/>
+      <c r="G76" s="149" t="n"/>
+      <c r="H76" s="155" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1" s="41">
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="33" t="n"/>
-      <c r="D77" s="33" t="n"/>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="4" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="6" t="n"/>
+      <c r="B77" s="34" t="n"/>
+      <c r="C77" s="1" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="35" t="n"/>
+      <c r="F77" s="154" t="n"/>
+      <c r="G77" s="149" t="n"/>
+      <c r="H77" s="155" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1" s="41">
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="33" t="n"/>
-      <c r="D78" s="33" t="n"/>
-      <c r="E78" s="7" t="n"/>
-      <c r="F78" s="4" t="n"/>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="6" t="n"/>
+      <c r="B78" s="34" t="n"/>
+      <c r="C78" s="1" t="n"/>
+      <c r="D78" s="1" t="n"/>
+      <c r="E78" s="35" t="n"/>
+      <c r="F78" s="154" t="n"/>
+      <c r="G78" s="149" t="n"/>
+      <c r="H78" s="155" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1" s="41">
-      <c r="B79" s="11" t="n"/>
-      <c r="C79" s="33" t="n"/>
-      <c r="D79" s="33" t="n"/>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="4" t="n"/>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="6" t="n"/>
+      <c r="B79" s="34" t="n"/>
+      <c r="C79" s="1" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="35" t="n"/>
+      <c r="F79" s="154" t="n"/>
+      <c r="G79" s="149" t="n"/>
+      <c r="H79" s="155" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1" s="41">
-      <c r="B80" s="11" t="n"/>
-      <c r="C80" s="33" t="n"/>
-      <c r="D80" s="33" t="n"/>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="6" t="n"/>
+      <c r="B80" s="34" t="n"/>
+      <c r="C80" s="1" t="n"/>
+      <c r="D80" s="1" t="n"/>
+      <c r="E80" s="35" t="n"/>
+      <c r="F80" s="154" t="n"/>
+      <c r="G80" s="149" t="n"/>
+      <c r="H80" s="155" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1" s="41">
-      <c r="B81" s="11" t="n"/>
-      <c r="C81" s="33" t="n"/>
-      <c r="D81" s="33" t="n"/>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="6" t="n"/>
+      <c r="B81" s="34" t="n"/>
+      <c r="C81" s="1" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="35" t="n"/>
+      <c r="F81" s="154" t="n"/>
+      <c r="G81" s="149" t="n"/>
+      <c r="H81" s="155" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1" s="41">
-      <c r="B82" s="11" t="n"/>
-      <c r="C82" s="33" t="n"/>
-      <c r="D82" s="33" t="n"/>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="4" t="n"/>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="6" t="n"/>
+      <c r="B82" s="34" t="n"/>
+      <c r="C82" s="1" t="n"/>
+      <c r="D82" s="1" t="n"/>
+      <c r="E82" s="35" t="n"/>
+      <c r="F82" s="154" t="n"/>
+      <c r="G82" s="149" t="n"/>
+      <c r="H82" s="155" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1" s="41">
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="33" t="n"/>
-      <c r="D83" s="33" t="n"/>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="6" t="n"/>
+      <c r="B83" s="34" t="n"/>
+      <c r="C83" s="1" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="35" t="n"/>
+      <c r="F83" s="154" t="n"/>
+      <c r="G83" s="149" t="n"/>
+      <c r="H83" s="155" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1" s="41">
-      <c r="B84" s="11" t="n"/>
-      <c r="C84" s="33" t="n"/>
-      <c r="D84" s="33" t="n"/>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="6" t="n"/>
+      <c r="B84" s="34" t="n"/>
+      <c r="C84" s="1" t="n"/>
+      <c r="D84" s="1" t="n"/>
+      <c r="E84" s="35" t="n"/>
+      <c r="F84" s="154" t="n"/>
+      <c r="G84" s="149" t="n"/>
+      <c r="H84" s="155" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1" s="41">
-      <c r="B85" s="11" t="n"/>
-      <c r="C85" s="33" t="n"/>
-      <c r="D85" s="33" t="n"/>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="4" t="n"/>
-      <c r="G85" s="5" t="n"/>
-      <c r="H85" s="6" t="n"/>
+      <c r="B85" s="34" t="n"/>
+      <c r="C85" s="1" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="35" t="n"/>
+      <c r="F85" s="154" t="n"/>
+      <c r="G85" s="149" t="n"/>
+      <c r="H85" s="155" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1" s="41">
-      <c r="B86" s="11" t="n"/>
-      <c r="C86" s="33" t="n"/>
-      <c r="D86" s="33" t="n"/>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="5" t="n"/>
-      <c r="H86" s="6" t="n"/>
+      <c r="B86" s="34" t="n"/>
+      <c r="C86" s="1" t="n"/>
+      <c r="D86" s="1" t="n"/>
+      <c r="E86" s="35" t="n"/>
+      <c r="F86" s="154" t="n"/>
+      <c r="G86" s="149" t="n"/>
+      <c r="H86" s="155" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1" s="41">
-      <c r="B87" s="11" t="n"/>
-      <c r="C87" s="33" t="n"/>
-      <c r="D87" s="33" t="n"/>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="5" t="n"/>
-      <c r="H87" s="6" t="n"/>
+      <c r="B87" s="34" t="n"/>
+      <c r="C87" s="1" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="35" t="n"/>
+      <c r="F87" s="154" t="n"/>
+      <c r="G87" s="149" t="n"/>
+      <c r="H87" s="155" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1" s="41">
-      <c r="B88" s="11" t="n"/>
-      <c r="C88" s="33" t="n"/>
-      <c r="D88" s="33" t="n"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="4" t="n"/>
-      <c r="G88" s="5" t="n"/>
-      <c r="H88" s="6" t="n"/>
+      <c r="B88" s="34" t="n"/>
+      <c r="C88" s="1" t="n"/>
+      <c r="D88" s="1" t="n"/>
+      <c r="E88" s="35" t="n"/>
+      <c r="F88" s="154" t="n"/>
+      <c r="G88" s="149" t="n"/>
+      <c r="H88" s="155" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1" s="41">
-      <c r="B89" s="11" t="n"/>
-      <c r="C89" s="33" t="n"/>
-      <c r="D89" s="33" t="n"/>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="6" t="n"/>
+      <c r="B89" s="34" t="n"/>
+      <c r="C89" s="1" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="35" t="n"/>
+      <c r="F89" s="154" t="n"/>
+      <c r="G89" s="149" t="n"/>
+      <c r="H89" s="155" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1" s="41">
-      <c r="B90" s="11" t="n"/>
-      <c r="C90" s="33" t="n"/>
-      <c r="D90" s="33" t="n"/>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="4" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="6" t="n"/>
+      <c r="B90" s="34" t="n"/>
+      <c r="C90" s="1" t="n"/>
+      <c r="D90" s="1" t="n"/>
+      <c r="E90" s="35" t="n"/>
+      <c r="F90" s="154" t="n"/>
+      <c r="G90" s="149" t="n"/>
+      <c r="H90" s="155" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1" s="41">
-      <c r="B91" s="11" t="n"/>
-      <c r="C91" s="33" t="n"/>
-      <c r="D91" s="33" t="n"/>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="6" t="n"/>
+      <c r="B91" s="34" t="n"/>
+      <c r="C91" s="1" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="35" t="n"/>
+      <c r="F91" s="154" t="n"/>
+      <c r="G91" s="149" t="n"/>
+      <c r="H91" s="155" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1" s="41">
-      <c r="B92" s="11" t="n"/>
-      <c r="C92" s="33" t="n"/>
-      <c r="D92" s="33" t="n"/>
-      <c r="E92" s="7" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="6" t="n"/>
+      <c r="B92" s="34" t="n"/>
+      <c r="C92" s="1" t="n"/>
+      <c r="D92" s="1" t="n"/>
+      <c r="E92" s="35" t="n"/>
+      <c r="F92" s="154" t="n"/>
+      <c r="G92" s="149" t="n"/>
+      <c r="H92" s="155" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1" s="41">
-      <c r="B93" s="11" t="n"/>
-      <c r="C93" s="33" t="n"/>
-      <c r="D93" s="33" t="n"/>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="6" t="n"/>
+      <c r="B93" s="34" t="n"/>
+      <c r="C93" s="1" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="35" t="n"/>
+      <c r="F93" s="154" t="n"/>
+      <c r="G93" s="149" t="n"/>
+      <c r="H93" s="155" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1" s="41">
-      <c r="B94" s="11" t="n"/>
-      <c r="C94" s="33" t="n"/>
-      <c r="D94" s="33" t="n"/>
-      <c r="E94" s="7" t="n"/>
-      <c r="F94" s="4" t="n"/>
-      <c r="G94" s="5" t="n"/>
-      <c r="H94" s="6" t="n"/>
+      <c r="B94" s="34" t="n"/>
+      <c r="C94" s="1" t="n"/>
+      <c r="D94" s="1" t="n"/>
+      <c r="E94" s="35" t="n"/>
+      <c r="F94" s="154" t="n"/>
+      <c r="G94" s="149" t="n"/>
+      <c r="H94" s="155" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1" s="41">
-      <c r="B95" s="11" t="n"/>
-      <c r="C95" s="33" t="n"/>
-      <c r="D95" s="33" t="n"/>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="6" t="n"/>
+      <c r="B95" s="34" t="n"/>
+      <c r="C95" s="1" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="35" t="n"/>
+      <c r="F95" s="154" t="n"/>
+      <c r="G95" s="149" t="n"/>
+      <c r="H95" s="155" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1" s="41">
-      <c r="B96" s="11" t="n"/>
-      <c r="C96" s="33" t="n"/>
-      <c r="D96" s="33" t="n"/>
-      <c r="E96" s="7" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="5" t="n"/>
-      <c r="H96" s="6" t="n"/>
+      <c r="B96" s="34" t="n"/>
+      <c r="C96" s="1" t="n"/>
+      <c r="D96" s="1" t="n"/>
+      <c r="E96" s="35" t="n"/>
+      <c r="F96" s="154" t="n"/>
+      <c r="G96" s="149" t="n"/>
+      <c r="H96" s="155" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1" s="41">
-      <c r="B97" s="11" t="n"/>
-      <c r="C97" s="33" t="n"/>
-      <c r="D97" s="33" t="n"/>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="6" t="n"/>
+      <c r="B97" s="34" t="n"/>
+      <c r="C97" s="1" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="35" t="n"/>
+      <c r="F97" s="154" t="n"/>
+      <c r="G97" s="149" t="n"/>
+      <c r="H97" s="155" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1" s="41">
-      <c r="B98" s="11" t="n"/>
-      <c r="C98" s="33" t="n"/>
-      <c r="D98" s="33" t="n"/>
-      <c r="E98" s="7" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="5" t="n"/>
-      <c r="H98" s="6" t="n"/>
+      <c r="B98" s="34" t="n"/>
+      <c r="C98" s="1" t="n"/>
+      <c r="D98" s="1" t="n"/>
+      <c r="E98" s="35" t="n"/>
+      <c r="F98" s="154" t="n"/>
+      <c r="G98" s="149" t="n"/>
+      <c r="H98" s="155" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1" s="41">
-      <c r="B99" s="11" t="n"/>
-      <c r="C99" s="33" t="n"/>
-      <c r="D99" s="33" t="n"/>
-      <c r="E99" s="7" t="n"/>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="5" t="n"/>
-      <c r="H99" s="6" t="n"/>
+      <c r="B99" s="34" t="n"/>
+      <c r="C99" s="1" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="35" t="n"/>
+      <c r="F99" s="154" t="n"/>
+      <c r="G99" s="149" t="n"/>
+      <c r="H99" s="155" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1" s="41">
-      <c r="B100" s="11" t="n"/>
-      <c r="C100" s="33" t="n"/>
-      <c r="D100" s="33" t="n"/>
-      <c r="E100" s="7" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="6" t="n"/>
+      <c r="B100" s="34" t="n"/>
+      <c r="C100" s="1" t="n"/>
+      <c r="D100" s="1" t="n"/>
+      <c r="E100" s="35" t="n"/>
+      <c r="F100" s="154" t="n"/>
+      <c r="G100" s="149" t="n"/>
+      <c r="H100" s="155" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1" s="41">
-      <c r="B101" s="11" t="n"/>
-      <c r="C101" s="33" t="n"/>
-      <c r="D101" s="33" t="n"/>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="6" t="n"/>
+      <c r="B101" s="34" t="n"/>
+      <c r="C101" s="1" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="35" t="n"/>
+      <c r="F101" s="154" t="n"/>
+      <c r="G101" s="149" t="n"/>
+      <c r="H101" s="155" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1" s="41">
-      <c r="B102" s="11" t="n"/>
-      <c r="C102" s="33" t="n"/>
-      <c r="D102" s="33" t="n"/>
-      <c r="E102" s="7" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="5" t="n"/>
-      <c r="H102" s="6" t="n"/>
+      <c r="B102" s="34" t="n"/>
+      <c r="C102" s="1" t="n"/>
+      <c r="D102" s="1" t="n"/>
+      <c r="E102" s="35" t="n"/>
+      <c r="F102" s="154" t="n"/>
+      <c r="G102" s="149" t="n"/>
+      <c r="H102" s="155" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1" s="41">
-      <c r="B103" s="11" t="n"/>
-      <c r="C103" s="33" t="n"/>
-      <c r="D103" s="33" t="n"/>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="4" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="6" t="n"/>
+      <c r="B103" s="34" t="n"/>
+      <c r="C103" s="1" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="35" t="n"/>
+      <c r="F103" s="154" t="n"/>
+      <c r="G103" s="149" t="n"/>
+      <c r="H103" s="155" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1" s="41">
-      <c r="B104" s="11" t="n"/>
-      <c r="C104" s="33" t="n"/>
-      <c r="D104" s="33" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="4" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="6" t="n"/>
+      <c r="B104" s="34" t="n"/>
+      <c r="C104" s="1" t="n"/>
+      <c r="D104" s="1" t="n"/>
+      <c r="E104" s="35" t="n"/>
+      <c r="F104" s="154" t="n"/>
+      <c r="G104" s="149" t="n"/>
+      <c r="H104" s="155" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1" s="41">
-      <c r="B105" s="11" t="n"/>
-      <c r="C105" s="33" t="n"/>
-      <c r="D105" s="33" t="n"/>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="4" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="6" t="n"/>
+      <c r="B105" s="34" t="n"/>
+      <c r="C105" s="1" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="35" t="n"/>
+      <c r="F105" s="154" t="n"/>
+      <c r="G105" s="149" t="n"/>
+      <c r="H105" s="155" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1" s="41">
-      <c r="B106" s="11" t="n"/>
-      <c r="C106" s="33" t="n"/>
-      <c r="D106" s="33" t="n"/>
-      <c r="E106" s="7" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="6" t="n"/>
+      <c r="B106" s="34" t="n"/>
+      <c r="C106" s="1" t="n"/>
+      <c r="D106" s="1" t="n"/>
+      <c r="E106" s="35" t="n"/>
+      <c r="F106" s="154" t="n"/>
+      <c r="G106" s="149" t="n"/>
+      <c r="H106" s="155" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1" s="41">
-      <c r="B107" s="11" t="n"/>
-      <c r="C107" s="33" t="n"/>
-      <c r="D107" s="33" t="n"/>
-      <c r="E107" s="7" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="5" t="n"/>
-      <c r="H107" s="6" t="n"/>
+      <c r="B107" s="34" t="n"/>
+      <c r="C107" s="1" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="35" t="n"/>
+      <c r="F107" s="154" t="n"/>
+      <c r="G107" s="149" t="n"/>
+      <c r="H107" s="155" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1" s="41">
-      <c r="B108" s="11" t="n"/>
-      <c r="C108" s="33" t="n"/>
-      <c r="D108" s="33" t="n"/>
-      <c r="E108" s="7" t="n"/>
-      <c r="F108" s="4" t="n"/>
-      <c r="G108" s="5" t="n"/>
-      <c r="H108" s="6" t="n"/>
+      <c r="B108" s="34" t="n"/>
+      <c r="C108" s="1" t="n"/>
+      <c r="D108" s="1" t="n"/>
+      <c r="E108" s="35" t="n"/>
+      <c r="F108" s="154" t="n"/>
+      <c r="G108" s="149" t="n"/>
+      <c r="H108" s="155" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1" s="41">
-      <c r="B109" s="11" t="n"/>
-      <c r="C109" s="33" t="n"/>
-      <c r="D109" s="33" t="n"/>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="4" t="n"/>
-      <c r="G109" s="5" t="n"/>
-      <c r="H109" s="6" t="n"/>
+      <c r="B109" s="34" t="n"/>
+      <c r="C109" s="1" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="35" t="n"/>
+      <c r="F109" s="154" t="n"/>
+      <c r="G109" s="149" t="n"/>
+      <c r="H109" s="155" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1" s="41">
-      <c r="B110" s="11" t="n"/>
-      <c r="C110" s="33" t="n"/>
-      <c r="D110" s="33" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="5" t="n"/>
-      <c r="H110" s="6" t="n"/>
+      <c r="B110" s="34" t="n"/>
+      <c r="C110" s="1" t="n"/>
+      <c r="D110" s="1" t="n"/>
+      <c r="E110" s="35" t="n"/>
+      <c r="F110" s="154" t="n"/>
+      <c r="G110" s="149" t="n"/>
+      <c r="H110" s="155" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1" s="41">
-      <c r="B111" s="11" t="n"/>
-      <c r="C111" s="33" t="n"/>
-      <c r="D111" s="33" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="4" t="n"/>
-      <c r="G111" s="5" t="n"/>
-      <c r="H111" s="6" t="n"/>
+      <c r="B111" s="34" t="n"/>
+      <c r="C111" s="1" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="35" t="n"/>
+      <c r="F111" s="154" t="n"/>
+      <c r="G111" s="149" t="n"/>
+      <c r="H111" s="155" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1" s="41">
-      <c r="B112" s="11" t="n"/>
-      <c r="C112" s="33" t="n"/>
-      <c r="D112" s="33" t="n"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="4" t="n"/>
-      <c r="G112" s="5" t="n"/>
-      <c r="H112" s="6" t="n"/>
+      <c r="B112" s="34" t="n"/>
+      <c r="C112" s="1" t="n"/>
+      <c r="D112" s="1" t="n"/>
+      <c r="E112" s="35" t="n"/>
+      <c r="F112" s="154" t="n"/>
+      <c r="G112" s="149" t="n"/>
+      <c r="H112" s="155" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1" s="41">
-      <c r="B113" s="11" t="n"/>
-      <c r="C113" s="33" t="n"/>
-      <c r="D113" s="33" t="n"/>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="5" t="n"/>
-      <c r="H113" s="6" t="n"/>
+      <c r="B113" s="34" t="n"/>
+      <c r="C113" s="1" t="n"/>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="35" t="n"/>
+      <c r="F113" s="154" t="n"/>
+      <c r="G113" s="149" t="n"/>
+      <c r="H113" s="155" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1" s="41">
-      <c r="B114" s="11" t="n"/>
-      <c r="C114" s="33" t="n"/>
-      <c r="D114" s="33" t="n"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="5" t="n"/>
-      <c r="H114" s="6" t="n"/>
+      <c r="B114" s="34" t="n"/>
+      <c r="C114" s="1" t="n"/>
+      <c r="D114" s="1" t="n"/>
+      <c r="E114" s="35" t="n"/>
+      <c r="F114" s="154" t="n"/>
+      <c r="G114" s="149" t="n"/>
+      <c r="H114" s="155" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1" s="41">
-      <c r="B115" s="11" t="n"/>
-      <c r="C115" s="33" t="n"/>
-      <c r="D115" s="33" t="n"/>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="4" t="n"/>
-      <c r="G115" s="5" t="n"/>
-      <c r="H115" s="6" t="n"/>
+      <c r="B115" s="34" t="n"/>
+      <c r="C115" s="1" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="35" t="n"/>
+      <c r="F115" s="154" t="n"/>
+      <c r="G115" s="149" t="n"/>
+      <c r="H115" s="155" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1" s="41">
-      <c r="B116" s="11" t="n"/>
-      <c r="C116" s="33" t="n"/>
-      <c r="D116" s="33" t="n"/>
-      <c r="E116" s="7" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="5" t="n"/>
-      <c r="H116" s="6" t="n"/>
+      <c r="B116" s="34" t="n"/>
+      <c r="C116" s="1" t="n"/>
+      <c r="D116" s="1" t="n"/>
+      <c r="E116" s="35" t="n"/>
+      <c r="F116" s="154" t="n"/>
+      <c r="G116" s="149" t="n"/>
+      <c r="H116" s="155" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1" s="41">
-      <c r="B117" s="11" t="n"/>
-      <c r="C117" s="33" t="n"/>
-      <c r="D117" s="33" t="n"/>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="4" t="n"/>
-      <c r="G117" s="5" t="n"/>
-      <c r="H117" s="6" t="n"/>
+      <c r="B117" s="34" t="n"/>
+      <c r="C117" s="1" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="35" t="n"/>
+      <c r="F117" s="154" t="n"/>
+      <c r="G117" s="149" t="n"/>
+      <c r="H117" s="155" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1" s="41">
-      <c r="B118" s="11" t="n"/>
-      <c r="C118" s="33" t="n"/>
-      <c r="D118" s="33" t="n"/>
-      <c r="E118" s="7" t="n"/>
-      <c r="F118" s="4" t="n"/>
-      <c r="G118" s="5" t="n"/>
-      <c r="H118" s="6" t="n"/>
+      <c r="B118" s="34" t="n"/>
+      <c r="C118" s="1" t="n"/>
+      <c r="D118" s="1" t="n"/>
+      <c r="E118" s="35" t="n"/>
+      <c r="F118" s="154" t="n"/>
+      <c r="G118" s="149" t="n"/>
+      <c r="H118" s="155" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1" s="41">
-      <c r="B119" s="11" t="n"/>
-      <c r="C119" s="33" t="n"/>
-      <c r="D119" s="33" t="n"/>
-      <c r="E119" s="7" t="n"/>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="5" t="n"/>
-      <c r="H119" s="6" t="n"/>
+      <c r="B119" s="34" t="n"/>
+      <c r="C119" s="1" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="35" t="n"/>
+      <c r="F119" s="154" t="n"/>
+      <c r="G119" s="149" t="n"/>
+      <c r="H119" s="155" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1" s="41">
-      <c r="B120" s="11" t="n"/>
-      <c r="C120" s="33" t="n"/>
-      <c r="D120" s="33" t="n"/>
-      <c r="E120" s="7" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="5" t="n"/>
-      <c r="H120" s="6" t="n"/>
+      <c r="B120" s="34" t="n"/>
+      <c r="C120" s="1" t="n"/>
+      <c r="D120" s="1" t="n"/>
+      <c r="E120" s="35" t="n"/>
+      <c r="F120" s="154" t="n"/>
+      <c r="G120" s="149" t="n"/>
+      <c r="H120" s="155" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1" s="41">
-      <c r="B121" s="11" t="n"/>
-      <c r="C121" s="33" t="n"/>
-      <c r="D121" s="33" t="n"/>
-      <c r="E121" s="7" t="n"/>
-      <c r="F121" s="4" t="n"/>
-      <c r="G121" s="5" t="n"/>
-      <c r="H121" s="6" t="n"/>
+      <c r="B121" s="34" t="n"/>
+      <c r="C121" s="1" t="n"/>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="35" t="n"/>
+      <c r="F121" s="154" t="n"/>
+      <c r="G121" s="149" t="n"/>
+      <c r="H121" s="155" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1" s="41">
-      <c r="B122" s="11" t="n"/>
-      <c r="C122" s="33" t="n"/>
-      <c r="D122" s="33" t="n"/>
-      <c r="E122" s="7" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="5" t="n"/>
-      <c r="H122" s="6" t="n"/>
+      <c r="B122" s="34" t="n"/>
+      <c r="C122" s="1" t="n"/>
+      <c r="D122" s="1" t="n"/>
+      <c r="E122" s="35" t="n"/>
+      <c r="F122" s="154" t="n"/>
+      <c r="G122" s="149" t="n"/>
+      <c r="H122" s="155" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1" s="41">
-      <c r="B123" s="11" t="n"/>
-      <c r="C123" s="33" t="n"/>
-      <c r="D123" s="33" t="n"/>
-      <c r="E123" s="7" t="n"/>
-      <c r="F123" s="4" t="n"/>
-      <c r="G123" s="5" t="n"/>
-      <c r="H123" s="6" t="n"/>
+      <c r="B123" s="34" t="n"/>
+      <c r="C123" s="1" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="35" t="n"/>
+      <c r="F123" s="154" t="n"/>
+      <c r="G123" s="149" t="n"/>
+      <c r="H123" s="155" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1" s="41">
-      <c r="B124" s="11" t="n"/>
-      <c r="C124" s="33" t="n"/>
-      <c r="D124" s="33" t="n"/>
-      <c r="E124" s="7" t="n"/>
-      <c r="F124" s="4" t="n"/>
-      <c r="G124" s="5" t="n"/>
-      <c r="H124" s="6" t="n"/>
+      <c r="B124" s="34" t="n"/>
+      <c r="C124" s="1" t="n"/>
+      <c r="D124" s="1" t="n"/>
+      <c r="E124" s="35" t="n"/>
+      <c r="F124" s="154" t="n"/>
+      <c r="G124" s="149" t="n"/>
+      <c r="H124" s="155" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="34" t="n"/>
+      <c r="C125" s="1" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="35" t="n"/>
+      <c r="F125" s="154" t="n"/>
+      <c r="G125" s="149" t="n"/>
+      <c r="H125" s="155" t="n"/>
     </row>
     <row r="126">
-      <c r="B126" s="65" t="inlineStr">
+      <c r="B126" s="34" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="C126" s="145" t="n"/>
-      <c r="D126" s="145" t="n"/>
-      <c r="E126" s="146" t="n"/>
-      <c r="F126" s="9">
+      <c r="C126" s="156" t="n"/>
+      <c r="D126" s="156" t="n"/>
+      <c r="E126" s="157" t="n"/>
+      <c r="F126" s="154">
         <f>SUM(F6:F125)</f>
         <v/>
       </c>
-      <c r="G126" s="9">
+      <c r="G126" s="149">
         <f>SUM(G6:G125)</f>
         <v/>
       </c>
-      <c r="H126" s="9">
+      <c r="H126" s="155">
         <f>SUM(H6:H125)</f>
         <v/>
       </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="34" t="n"/>
+      <c r="C127" s="1" t="n"/>
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="35" t="n"/>
+      <c r="F127" s="154" t="n"/>
+      <c r="G127" s="149" t="n"/>
+      <c r="H127" s="155" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="34" t="n"/>
+      <c r="C128" s="1" t="n"/>
+      <c r="D128" s="1" t="n"/>
+      <c r="E128" s="35" t="n"/>
+      <c r="F128" s="154" t="n"/>
+      <c r="G128" s="149" t="n"/>
+      <c r="H128" s="155" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="34" t="n"/>
+      <c r="C129" s="1" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="35" t="n"/>
+      <c r="F129" s="154" t="n"/>
+      <c r="G129" s="149" t="n"/>
+      <c r="H129" s="155" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="34" t="n"/>
+      <c r="C130" s="1" t="n"/>
+      <c r="D130" s="1" t="n"/>
+      <c r="E130" s="35" t="n"/>
+      <c r="F130" s="154" t="n"/>
+      <c r="G130" s="149" t="n"/>
+      <c r="H130" s="155" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="34" t="n"/>
+      <c r="C131" s="1" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="35" t="n"/>
+      <c r="F131" s="154" t="n"/>
+      <c r="G131" s="149" t="n"/>
+      <c r="H131" s="155" t="n"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="34" t="n"/>
+      <c r="C132" s="1" t="n"/>
+      <c r="D132" s="1" t="n"/>
+      <c r="E132" s="35" t="n"/>
+      <c r="F132" s="154" t="n"/>
+      <c r="G132" s="149" t="n"/>
+      <c r="H132" s="155" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="34" t="n"/>
+      <c r="C133" s="1" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="35" t="n"/>
+      <c r="F133" s="154" t="n"/>
+      <c r="G133" s="149" t="n"/>
+      <c r="H133" s="155" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="34" t="n"/>
+      <c r="C134" s="1" t="n"/>
+      <c r="D134" s="1" t="n"/>
+      <c r="E134" s="35" t="n"/>
+      <c r="F134" s="154" t="n"/>
+      <c r="G134" s="149" t="n"/>
+      <c r="H134" s="155" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="34" t="n"/>
+      <c r="C135" s="1" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="35" t="n"/>
+      <c r="F135" s="154" t="n"/>
+      <c r="G135" s="149" t="n"/>
+      <c r="H135" s="155" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="34" t="n"/>
+      <c r="C136" s="1" t="n"/>
+      <c r="D136" s="1" t="n"/>
+      <c r="E136" s="35" t="n"/>
+      <c r="F136" s="154" t="n"/>
+      <c r="G136" s="149" t="n"/>
+      <c r="H136" s="155" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="34" t="n"/>
+      <c r="C137" s="1" t="n"/>
+      <c r="D137" s="8" t="n"/>
+      <c r="E137" s="35" t="n"/>
+      <c r="F137" s="154" t="n"/>
+      <c r="G137" s="149" t="n"/>
+      <c r="H137" s="155" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="34" t="n"/>
+      <c r="C138" s="1" t="n"/>
+      <c r="D138" s="1" t="n"/>
+      <c r="E138" s="35" t="n"/>
+      <c r="F138" s="154" t="n"/>
+      <c r="G138" s="149" t="n"/>
+      <c r="H138" s="155" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="34" t="n"/>
+      <c r="C139" s="1" t="n"/>
+      <c r="D139" s="8" t="n"/>
+      <c r="E139" s="35" t="n"/>
+      <c r="F139" s="154" t="n"/>
+      <c r="G139" s="149" t="n"/>
+      <c r="H139" s="155" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="34" t="n"/>
+      <c r="C140" s="1" t="n"/>
+      <c r="D140" s="1" t="n"/>
+      <c r="E140" s="35" t="n"/>
+      <c r="F140" s="154" t="n"/>
+      <c r="G140" s="149" t="n"/>
+      <c r="H140" s="155" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="34" t="n"/>
+      <c r="C141" s="1" t="n"/>
+      <c r="D141" s="8" t="n"/>
+      <c r="E141" s="35" t="n"/>
+      <c r="F141" s="154" t="n"/>
+      <c r="G141" s="149" t="n"/>
+      <c r="H141" s="155" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="34" t="n"/>
+      <c r="C142" s="1" t="n"/>
+      <c r="D142" s="1" t="n"/>
+      <c r="E142" s="35" t="n"/>
+      <c r="F142" s="154" t="n"/>
+      <c r="G142" s="149" t="n"/>
+      <c r="H142" s="155" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="34" t="n"/>
+      <c r="C143" s="1" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="35" t="n"/>
+      <c r="F143" s="154" t="n"/>
+      <c r="G143" s="149" t="n"/>
+      <c r="H143" s="155" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="34" t="n"/>
+      <c r="C144" s="1" t="n"/>
+      <c r="D144" s="1" t="n"/>
+      <c r="E144" s="35" t="n"/>
+      <c r="F144" s="154" t="n"/>
+      <c r="G144" s="149" t="n"/>
+      <c r="H144" s="155" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="34" t="n"/>
+      <c r="C145" s="1" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="35" t="n"/>
+      <c r="F145" s="154" t="n"/>
+      <c r="G145" s="149" t="n"/>
+      <c r="H145" s="155" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="34" t="n"/>
+      <c r="C146" s="1" t="n"/>
+      <c r="D146" s="1" t="n"/>
+      <c r="E146" s="35" t="n"/>
+      <c r="F146" s="154" t="n"/>
+      <c r="G146" s="149" t="n"/>
+      <c r="H146" s="155" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="34" t="n"/>
+      <c r="C147" s="1" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="35" t="n"/>
+      <c r="F147" s="154" t="n"/>
+      <c r="G147" s="149" t="n"/>
+      <c r="H147" s="155" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="34" t="n"/>
+      <c r="C148" s="1" t="n"/>
+      <c r="D148" s="1" t="n"/>
+      <c r="E148" s="35" t="n"/>
+      <c r="F148" s="154" t="n"/>
+      <c r="G148" s="149" t="n"/>
+      <c r="H148" s="155" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="34" t="n"/>
+      <c r="C149" s="1" t="n"/>
+      <c r="D149" s="8" t="n"/>
+      <c r="E149" s="35" t="n"/>
+      <c r="F149" s="154" t="n"/>
+      <c r="G149" s="149" t="n"/>
+      <c r="H149" s="155" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="34" t="n"/>
+      <c r="C150" s="1" t="n"/>
+      <c r="D150" s="1" t="n"/>
+      <c r="E150" s="35" t="n"/>
+      <c r="F150" s="154" t="n"/>
+      <c r="G150" s="149" t="n"/>
+      <c r="H150" s="155" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="34" t="n"/>
+      <c r="C151" s="1" t="n"/>
+      <c r="D151" s="8" t="n"/>
+      <c r="E151" s="35" t="n"/>
+      <c r="F151" s="154" t="n"/>
+      <c r="G151" s="149" t="n"/>
+      <c r="H151" s="155" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="34" t="n"/>
+      <c r="C152" s="1" t="n"/>
+      <c r="D152" s="1" t="n"/>
+      <c r="E152" s="35" t="n"/>
+      <c r="F152" s="154" t="n"/>
+      <c r="G152" s="149" t="n"/>
+      <c r="H152" s="155" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="34" t="n"/>
+      <c r="C153" s="1" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="35" t="n"/>
+      <c r="F153" s="154" t="n"/>
+      <c r="G153" s="149" t="n"/>
+      <c r="H153" s="155" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="34" t="n"/>
+      <c r="C154" s="1" t="n"/>
+      <c r="D154" s="1" t="n"/>
+      <c r="E154" s="35" t="n"/>
+      <c r="F154" s="154" t="n"/>
+      <c r="G154" s="149" t="n"/>
+      <c r="H154" s="155" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="34" t="n"/>
+      <c r="C155" s="1" t="n"/>
+      <c r="D155" s="8" t="n"/>
+      <c r="E155" s="35" t="n"/>
+      <c r="F155" s="154" t="n"/>
+      <c r="G155" s="149" t="n"/>
+      <c r="H155" s="155" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="34" t="n"/>
+      <c r="C156" s="1" t="n"/>
+      <c r="D156" s="1" t="n"/>
+      <c r="E156" s="35" t="n"/>
+      <c r="F156" s="154" t="n"/>
+      <c r="G156" s="149" t="n"/>
+      <c r="H156" s="155" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="34" t="n"/>
+      <c r="C157" s="1" t="n"/>
+      <c r="D157" s="8" t="n"/>
+      <c r="E157" s="35" t="n"/>
+      <c r="F157" s="154" t="n"/>
+      <c r="G157" s="149" t="n"/>
+      <c r="H157" s="155" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="34" t="n"/>
+      <c r="C158" s="1" t="n"/>
+      <c r="D158" s="1" t="n"/>
+      <c r="E158" s="35" t="n"/>
+      <c r="F158" s="154" t="n"/>
+      <c r="G158" s="149" t="n"/>
+      <c r="H158" s="155" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="34" t="n"/>
+      <c r="C159" s="1" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="35" t="n"/>
+      <c r="F159" s="154" t="n"/>
+      <c r="G159" s="149" t="n"/>
+      <c r="H159" s="155" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="34" t="n"/>
+      <c r="C160" s="1" t="n"/>
+      <c r="D160" s="1" t="n"/>
+      <c r="E160" s="35" t="n"/>
+      <c r="F160" s="154" t="n"/>
+      <c r="G160" s="149" t="n"/>
+      <c r="H160" s="155" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="34" t="n"/>
+      <c r="C161" s="1" t="n"/>
+      <c r="D161" s="8" t="n"/>
+      <c r="E161" s="35" t="n"/>
+      <c r="F161" s="154" t="n"/>
+      <c r="G161" s="149" t="n"/>
+      <c r="H161" s="155" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="34" t="n"/>
+      <c r="C162" s="1" t="n"/>
+      <c r="D162" s="1" t="n"/>
+      <c r="E162" s="35" t="n"/>
+      <c r="F162" s="154" t="n"/>
+      <c r="G162" s="149" t="n"/>
+      <c r="H162" s="155" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="34" t="n"/>
+      <c r="C163" s="1" t="n"/>
+      <c r="D163" s="8" t="n"/>
+      <c r="E163" s="35" t="n"/>
+      <c r="F163" s="154" t="n"/>
+      <c r="G163" s="149" t="n"/>
+      <c r="H163" s="155" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="34" t="n"/>
+      <c r="C164" s="1" t="n"/>
+      <c r="D164" s="1" t="n"/>
+      <c r="E164" s="35" t="n"/>
+      <c r="F164" s="154" t="n"/>
+      <c r="G164" s="149" t="n"/>
+      <c r="H164" s="155" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="34" t="n"/>
+      <c r="C165" s="1" t="n"/>
+      <c r="D165" s="8" t="n"/>
+      <c r="E165" s="35" t="n"/>
+      <c r="F165" s="154" t="n"/>
+      <c r="G165" s="149" t="n"/>
+      <c r="H165" s="155" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="34" t="n"/>
+      <c r="C166" s="1" t="n"/>
+      <c r="D166" s="1" t="n"/>
+      <c r="E166" s="35" t="n"/>
+      <c r="F166" s="154" t="n"/>
+      <c r="G166" s="149" t="n"/>
+      <c r="H166" s="155" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="34" t="n"/>
+      <c r="C167" s="1" t="n"/>
+      <c r="D167" s="8" t="n"/>
+      <c r="E167" s="35" t="n"/>
+      <c r="F167" s="154" t="n"/>
+      <c r="G167" s="149" t="n"/>
+      <c r="H167" s="155" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="34" t="n"/>
+      <c r="C168" s="1" t="n"/>
+      <c r="D168" s="1" t="n"/>
+      <c r="E168" s="35" t="n"/>
+      <c r="F168" s="154" t="n"/>
+      <c r="G168" s="149" t="n"/>
+      <c r="H168" s="155" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="34" t="n"/>
+      <c r="C169" s="1" t="n"/>
+      <c r="D169" s="8" t="n"/>
+      <c r="E169" s="35" t="n"/>
+      <c r="F169" s="154" t="n"/>
+      <c r="G169" s="149" t="n"/>
+      <c r="H169" s="155" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="34" t="n"/>
+      <c r="C170" s="1" t="n"/>
+      <c r="D170" s="1" t="n"/>
+      <c r="E170" s="35" t="n"/>
+      <c r="F170" s="154" t="n"/>
+      <c r="G170" s="149" t="n"/>
+      <c r="H170" s="155" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="34" t="n"/>
+      <c r="C171" s="1" t="n"/>
+      <c r="D171" s="8" t="n"/>
+      <c r="E171" s="35" t="n"/>
+      <c r="F171" s="154" t="n"/>
+      <c r="G171" s="149" t="n"/>
+      <c r="H171" s="155" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="34" t="n"/>
+      <c r="C172" s="1" t="n"/>
+      <c r="D172" s="1" t="n"/>
+      <c r="E172" s="35" t="n"/>
+      <c r="F172" s="154" t="n"/>
+      <c r="G172" s="149" t="n"/>
+      <c r="H172" s="155" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="34" t="n"/>
+      <c r="C173" s="1" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="35" t="n"/>
+      <c r="F173" s="154" t="n"/>
+      <c r="G173" s="149" t="n"/>
+      <c r="H173" s="155" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="34" t="n"/>
+      <c r="C174" s="1" t="n"/>
+      <c r="D174" s="1" t="n"/>
+      <c r="E174" s="35" t="n"/>
+      <c r="F174" s="154" t="n"/>
+      <c r="G174" s="149" t="n"/>
+      <c r="H174" s="155" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="34" t="n"/>
+      <c r="C175" s="1" t="n"/>
+      <c r="D175" s="8" t="n"/>
+      <c r="E175" s="35" t="n"/>
+      <c r="F175" s="154" t="n"/>
+      <c r="G175" s="149" t="n"/>
+      <c r="H175" s="155" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="34" t="n"/>
+      <c r="C176" s="1" t="n"/>
+      <c r="D176" s="1" t="n"/>
+      <c r="E176" s="35" t="n"/>
+      <c r="F176" s="154" t="n"/>
+      <c r="G176" s="149" t="n"/>
+      <c r="H176" s="155" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="34" t="n"/>
+      <c r="C177" s="1" t="n"/>
+      <c r="D177" s="8" t="n"/>
+      <c r="E177" s="35" t="n"/>
+      <c r="F177" s="154" t="n"/>
+      <c r="G177" s="149" t="n"/>
+      <c r="H177" s="155" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="34" t="n"/>
+      <c r="C178" s="1" t="n"/>
+      <c r="D178" s="1" t="n"/>
+      <c r="E178" s="35" t="n"/>
+      <c r="F178" s="154" t="n"/>
+      <c r="G178" s="149" t="n"/>
+      <c r="H178" s="155" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="34" t="n"/>
+      <c r="C179" s="1" t="n"/>
+      <c r="D179" s="8" t="n"/>
+      <c r="E179" s="35" t="n"/>
+      <c r="F179" s="154" t="n"/>
+      <c r="G179" s="149" t="n"/>
+      <c r="H179" s="155" t="n"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="34" t="n"/>
+      <c r="C180" s="1" t="n"/>
+      <c r="D180" s="1" t="n"/>
+      <c r="E180" s="35" t="n"/>
+      <c r="F180" s="154" t="n"/>
+      <c r="G180" s="149" t="n"/>
+      <c r="H180" s="155" t="n"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="34" t="n"/>
+      <c r="C181" s="1" t="n"/>
+      <c r="D181" s="8" t="n"/>
+      <c r="E181" s="35" t="n"/>
+      <c r="F181" s="154" t="n"/>
+      <c r="G181" s="149" t="n"/>
+      <c r="H181" s="155" t="n"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="34" t="n"/>
+      <c r="C182" s="1" t="n"/>
+      <c r="D182" s="1" t="n"/>
+      <c r="E182" s="35" t="n"/>
+      <c r="F182" s="154" t="n"/>
+      <c r="G182" s="149" t="n"/>
+      <c r="H182" s="155" t="n"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="34" t="n"/>
+      <c r="C183" s="1" t="n"/>
+      <c r="D183" s="8" t="n"/>
+      <c r="E183" s="35" t="n"/>
+      <c r="F183" s="154" t="n"/>
+      <c r="G183" s="149" t="n"/>
+      <c r="H183" s="155" t="n"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="34" t="n"/>
+      <c r="C184" s="1" t="n"/>
+      <c r="D184" s="1" t="n"/>
+      <c r="E184" s="35" t="n"/>
+      <c r="F184" s="154" t="n"/>
+      <c r="G184" s="149" t="n"/>
+      <c r="H184" s="155" t="n"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="34" t="n"/>
+      <c r="C185" s="1" t="n"/>
+      <c r="D185" s="8" t="n"/>
+      <c r="E185" s="35" t="n"/>
+      <c r="F185" s="154" t="n"/>
+      <c r="G185" s="149" t="n"/>
+      <c r="H185" s="155" t="n"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="34" t="n"/>
+      <c r="C186" s="1" t="n"/>
+      <c r="D186" s="1" t="n"/>
+      <c r="E186" s="35" t="n"/>
+      <c r="F186" s="154" t="n"/>
+      <c r="G186" s="149" t="n"/>
+      <c r="H186" s="155" t="n"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="34" t="n"/>
+      <c r="C187" s="1" t="n"/>
+      <c r="D187" s="8" t="n"/>
+      <c r="E187" s="35" t="n"/>
+      <c r="F187" s="154" t="n"/>
+      <c r="G187" s="149" t="n"/>
+      <c r="H187" s="155" t="n"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="34" t="n"/>
+      <c r="C188" s="1" t="n"/>
+      <c r="D188" s="1" t="n"/>
+      <c r="E188" s="35" t="n"/>
+      <c r="F188" s="154" t="n"/>
+      <c r="G188" s="149" t="n"/>
+      <c r="H188" s="155" t="n"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="34" t="n"/>
+      <c r="C189" s="1" t="n"/>
+      <c r="D189" s="8" t="n"/>
+      <c r="E189" s="35" t="n"/>
+      <c r="F189" s="154" t="n"/>
+      <c r="G189" s="149" t="n"/>
+      <c r="H189" s="155" t="n"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="34" t="n"/>
+      <c r="C190" s="1" t="n"/>
+      <c r="D190" s="1" t="n"/>
+      <c r="E190" s="35" t="n"/>
+      <c r="F190" s="154" t="n"/>
+      <c r="G190" s="149" t="n"/>
+      <c r="H190" s="155" t="n"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="34" t="n"/>
+      <c r="C191" s="1" t="n"/>
+      <c r="D191" s="8" t="n"/>
+      <c r="E191" s="35" t="n"/>
+      <c r="F191" s="154" t="n"/>
+      <c r="G191" s="149" t="n"/>
+      <c r="H191" s="155" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="34" t="n"/>
+      <c r="C192" s="1" t="n"/>
+      <c r="D192" s="1" t="n"/>
+      <c r="E192" s="35" t="n"/>
+      <c r="F192" s="154" t="n"/>
+      <c r="G192" s="149" t="n"/>
+      <c r="H192" s="155" t="n"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="34" t="n"/>
+      <c r="C193" s="1" t="n"/>
+      <c r="D193" s="8" t="n"/>
+      <c r="E193" s="35" t="n"/>
+      <c r="F193" s="154" t="n"/>
+      <c r="G193" s="149" t="n"/>
+      <c r="H193" s="155" t="n"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="34" t="n"/>
+      <c r="C194" s="1" t="n"/>
+      <c r="D194" s="1" t="n"/>
+      <c r="E194" s="35" t="n"/>
+      <c r="F194" s="154" t="n"/>
+      <c r="G194" s="149" t="n"/>
+      <c r="H194" s="155" t="n"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="34" t="n"/>
+      <c r="C195" s="1" t="n"/>
+      <c r="D195" s="8" t="n"/>
+      <c r="E195" s="35" t="n"/>
+      <c r="F195" s="154" t="n"/>
+      <c r="G195" s="149" t="n"/>
+      <c r="H195" s="155" t="n"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="34" t="n"/>
+      <c r="C196" s="1" t="n"/>
+      <c r="D196" s="1" t="n"/>
+      <c r="E196" s="35" t="n"/>
+      <c r="F196" s="154" t="n"/>
+      <c r="G196" s="149" t="n"/>
+      <c r="H196" s="155" t="n"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="34" t="n"/>
+      <c r="C197" s="1" t="n"/>
+      <c r="D197" s="8" t="n"/>
+      <c r="E197" s="35" t="n"/>
+      <c r="F197" s="154" t="n"/>
+      <c r="G197" s="149" t="n"/>
+      <c r="H197" s="155" t="n"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="34" t="n"/>
+      <c r="C198" s="1" t="n"/>
+      <c r="D198" s="1" t="n"/>
+      <c r="E198" s="35" t="n"/>
+      <c r="F198" s="154" t="n"/>
+      <c r="G198" s="149" t="n"/>
+      <c r="H198" s="155" t="n"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="34" t="n"/>
+      <c r="C199" s="1" t="n"/>
+      <c r="D199" s="8" t="n"/>
+      <c r="E199" s="35" t="n"/>
+      <c r="F199" s="154" t="n"/>
+      <c r="G199" s="149" t="n"/>
+      <c r="H199" s="155" t="n"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="34" t="n"/>
+      <c r="C200" s="1" t="n"/>
+      <c r="D200" s="1" t="n"/>
+      <c r="E200" s="35" t="n"/>
+      <c r="F200" s="154" t="n"/>
+      <c r="G200" s="149" t="n"/>
+      <c r="H200" s="155" t="n"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="34" t="n"/>
+      <c r="C201" s="1" t="n"/>
+      <c r="D201" s="8" t="n"/>
+      <c r="E201" s="35" t="n"/>
+      <c r="F201" s="154" t="n"/>
+      <c r="G201" s="149" t="n"/>
+      <c r="H201" s="155" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
